--- a/input/mapping/053. OCB_GOLD_TCKH_V_OPEX_DTL_ADJ_G_HOP.xlsx
+++ b/input/mapping/053. OCB_GOLD_TCKH_V_OPEX_DTL_ADJ_G_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3703" documentId="13_ncr:1_{2EFA5FB6-F35E-4DC0-AF69-F056B4784F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4457D41B-05F5-4184-A486-DC08E72E37BF}"/>
+  <xr:revisionPtr revIDLastSave="3706" documentId="13_ncr:1_{2EFA5FB6-F35E-4DC0-AF69-F056B4784F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86D042B5-915E-4085-9FA5-BE0C597A2CB5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -213,7 +213,6 @@
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
 CREATE OR REPLACE VIEW V_OPEX_DTL_ADJ_G AS
--- ── Block 1: OPEX_ADJ_DTL_UPL (alias a)
 SELECT
     a.MONTH_DATA,
     a.MONTH_DAY,
@@ -240,10 +239,7 @@
     a.CDR_DT_ID,
     a.DATA_DATE
 FROM OPEX_ADJ_DTL_UPL a
--- Không có WHERE — lấy toàn bộ
--- (WHERE CDR_DT_ID &gt;= 20240101 đã bị comment out trong DSX gốc)
 UNION ALL
--- ── Block 2: MANHINHPHI_DC_UPL (alias m)
 SELECT
     m.MONTH_DATA,
     m.MONTH_DAY,
@@ -270,8 +266,7 @@
     m.CDR_DT_ID,
     m.DATA_DATE
 FROM MANHINHPHI_DC_UPL m
-WHERE m.CDR_DT_ID BETWEEN 20190101 AND 20190731
-;</t>
+WHERE m.CDR_DT_ID BETWEEN 20190101 AND 20190731</t>
   </si>
   <si>
     <t>[ CREATE OR REPLACE VIEW ]  UNION ALL 4 blocks  →  V_OPEX_DTL  |  Block 1 (g): V_OPEX_DTL_G — TRUC TIEP, AR_ID='1000', MA_PHONG_G cắt sau '.'/'*'  |  Block 2 (a): V_ENTRY_STMT_8830 — BHTG SAOKE, AR_ID='1000', T_AMT_PBCP đảo dấu  |  Block 3 (j): V_OPEX_DTL_ADJ_G LINE='8830' — điều chỉnh BHTG  |  Block 4 (k): V_OPEX_DTL_ADJ_G LINE&lt;&gt;'8830' — điều chỉnh khác</t>
@@ -12664,10 +12659,40 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12712,11 +12737,23 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -12772,6 +12809,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -12789,42 +12832,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -12872,6 +12879,42 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13192,55 +13235,7 @@
     <xf numFmtId="0" fontId="23" fillId="23" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
@@ -13643,13 +13638,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="27.95" customHeight="1">
-      <c r="A1" s="253" t="s">
+      <c r="A1" s="264" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="253"/>
-      <c r="C1" s="253"/>
-      <c r="D1" s="253"/>
-      <c r="E1" s="253"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
       <c r="F1" s="251"/>
       <c r="G1" s="251"/>
       <c r="H1" s="251"/>
@@ -13671,51 +13666,50 @@
       <c r="X1" s="51"/>
     </row>
     <row r="2" spans="1:24" ht="18.75" customHeight="1">
-      <c r="A2" s="441" t="s">
+      <c r="A2" s="260" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="441"/>
-      <c r="C2" s="254" t="s">
+      <c r="B2" s="260"/>
+      <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="442" t="s">
+      <c r="D2" s="262" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="442"/>
-      <c r="F2" s="444"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="259"/>
     </row>
     <row r="3" spans="1:24" ht="15" customHeight="1">
-      <c r="A3" s="441"/>
-      <c r="B3" s="441"/>
-      <c r="C3" s="254"/>
-      <c r="D3" s="442"/>
-      <c r="E3" s="442"/>
-      <c r="F3" s="444"/>
+      <c r="A3" s="260"/>
+      <c r="B3" s="260"/>
+      <c r="C3" s="263"/>
+      <c r="D3" s="262"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="259"/>
     </row>
     <row r="4" spans="1:24" ht="16.5" customHeight="1">
-      <c r="A4" s="441"/>
-      <c r="B4" s="441"/>
-      <c r="F4" s="445"/>
+      <c r="A4" s="260"/>
+      <c r="B4" s="260"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1">
-      <c r="A5" s="441"/>
-      <c r="B5" s="441"/>
-      <c r="C5" s="254" t="s">
+      <c r="A5" s="260"/>
+      <c r="B5" s="260"/>
+      <c r="C5" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="442" t="s">
+      <c r="D5" s="262" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="442"/>
-      <c r="F5" s="444"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="259"/>
     </row>
     <row r="6" spans="1:24" ht="16.5" customHeight="1">
-      <c r="A6" s="443"/>
-      <c r="B6" s="443"/>
-      <c r="C6" s="254"/>
-      <c r="D6" s="442"/>
-      <c r="E6" s="442"/>
-      <c r="F6" s="444"/>
+      <c r="A6" s="261"/>
+      <c r="B6" s="261"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="262"/>
+      <c r="F6" s="259"/>
     </row>
     <row r="7" spans="1:24" ht="15.75">
       <c r="A7" s="250" t="s">
@@ -13828,12 +13822,12 @@
     <row r="59" ht="15"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:B6"/>
     <mergeCell ref="D2:E3"/>
     <mergeCell ref="D5:E6"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13853,14 +13847,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="308" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
+      <c r="B1" s="308"/>
+      <c r="C1" s="308"/>
+      <c r="D1" s="308"/>
+      <c r="E1" s="308"/>
+      <c r="F1" s="308"/>
     </row>
     <row r="2" spans="1:6" ht="30.75" customHeight="1">
       <c r="A2" s="252" t="s">
@@ -13875,10 +13869,10 @@
       <c r="D2" s="252" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="294" t="s">
+      <c r="E2" s="310" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="294"/>
+      <c r="F2" s="310"/>
     </row>
     <row r="3" spans="1:6" s="33" customFormat="1" ht="96.75" customHeight="1">
       <c r="A3" s="20">
@@ -13893,10 +13887,10 @@
       <c r="D3" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="E3" s="293" t="s">
+      <c r="E3" s="309" t="s">
         <v>302</v>
       </c>
-      <c r="F3" s="293"/>
+      <c r="F3" s="309"/>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="34"/>
@@ -13907,14 +13901,14 @@
       <c r="F4" s="34"/>
     </row>
     <row r="5" spans="1:6" ht="27" customHeight="1">
-      <c r="A5" s="271" t="s">
+      <c r="A5" s="285" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="272"/>
-      <c r="C5" s="272"/>
-      <c r="D5" s="272"/>
-      <c r="E5" s="272"/>
-      <c r="F5" s="272"/>
+      <c r="B5" s="286"/>
+      <c r="C5" s="286"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
+      <c r="F5" s="286"/>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" s="237" t="s">
@@ -19721,48 +19715,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="314" t="s">
         <v>1041</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="311"/>
-      <c r="G1" s="312"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="315"/>
+      <c r="G1" s="316"/>
     </row>
     <row r="2" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A2" s="313" t="s">
+      <c r="A2" s="317" t="s">
         <v>1042</v>
       </c>
-      <c r="B2" s="314"/>
-      <c r="C2" s="314"/>
-      <c r="D2" s="314"/>
-      <c r="E2" s="314"/>
-      <c r="F2" s="314"/>
-      <c r="G2" s="315"/>
+      <c r="B2" s="318"/>
+      <c r="C2" s="318"/>
+      <c r="D2" s="318"/>
+      <c r="E2" s="318"/>
+      <c r="F2" s="318"/>
+      <c r="G2" s="319"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="316" t="s">
+      <c r="A3" s="320" t="s">
         <v>1043</v>
       </c>
-      <c r="B3" s="317"/>
-      <c r="C3" s="317"/>
-      <c r="D3" s="317"/>
-      <c r="E3" s="317"/>
-      <c r="F3" s="317"/>
-      <c r="G3" s="318"/>
+      <c r="B3" s="321"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="322"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="319" t="s">
+      <c r="A4" s="323" t="s">
         <v>1044</v>
       </c>
-      <c r="B4" s="319"/>
-      <c r="C4" s="319"/>
-      <c r="D4" s="319"/>
-      <c r="E4" s="319"/>
-      <c r="F4" s="319"/>
-      <c r="G4" s="319"/>
+      <c r="B4" s="323"/>
+      <c r="C4" s="323"/>
+      <c r="D4" s="323"/>
+      <c r="E4" s="323"/>
+      <c r="F4" s="323"/>
+      <c r="G4" s="323"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1">
       <c r="A5" s="74" t="s">
@@ -19926,26 +19920,26 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A12" s="320" t="s">
-        <v>231</v>
-      </c>
-      <c r="B12" s="321"/>
-      <c r="C12" s="321"/>
-      <c r="D12" s="321"/>
-      <c r="E12" s="321"/>
-      <c r="F12" s="321"/>
-      <c r="G12" s="322"/>
+      <c r="A12" s="324" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="325"/>
+      <c r="C12" s="325"/>
+      <c r="D12" s="325"/>
+      <c r="E12" s="325"/>
+      <c r="F12" s="325"/>
+      <c r="G12" s="326"/>
     </row>
     <row r="13" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A13" s="307" t="s">
+      <c r="A13" s="311" t="s">
         <v>1067</v>
       </c>
-      <c r="B13" s="308"/>
-      <c r="C13" s="308"/>
-      <c r="D13" s="308"/>
-      <c r="E13" s="308"/>
-      <c r="F13" s="308"/>
-      <c r="G13" s="309"/>
+      <c r="B13" s="312"/>
+      <c r="C13" s="312"/>
+      <c r="D13" s="312"/>
+      <c r="E13" s="312"/>
+      <c r="F13" s="312"/>
+      <c r="G13" s="313"/>
     </row>
     <row r="14" spans="1:7" ht="43.5">
       <c r="A14" s="79" t="s">
@@ -19971,15 +19965,15 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A15" s="298" t="s">
+      <c r="A15" s="330" t="s">
         <v>1074</v>
       </c>
-      <c r="B15" s="299"/>
-      <c r="C15" s="299"/>
-      <c r="D15" s="299"/>
-      <c r="E15" s="299"/>
-      <c r="F15" s="299"/>
-      <c r="G15" s="300"/>
+      <c r="B15" s="331"/>
+      <c r="C15" s="331"/>
+      <c r="D15" s="331"/>
+      <c r="E15" s="331"/>
+      <c r="F15" s="331"/>
+      <c r="G15" s="332"/>
     </row>
     <row r="16" spans="1:7" ht="38.25">
       <c r="A16" s="83" t="s">
@@ -20465,15 +20459,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A37" s="301" t="s">
+      <c r="A37" s="333" t="s">
         <v>1104</v>
       </c>
-      <c r="B37" s="302"/>
-      <c r="C37" s="302"/>
-      <c r="D37" s="302"/>
-      <c r="E37" s="302"/>
-      <c r="F37" s="302"/>
-      <c r="G37" s="303"/>
+      <c r="B37" s="334"/>
+      <c r="C37" s="334"/>
+      <c r="D37" s="334"/>
+      <c r="E37" s="334"/>
+      <c r="F37" s="334"/>
+      <c r="G37" s="335"/>
     </row>
     <row r="38" spans="1:7" ht="38.25">
       <c r="A38" s="83" t="s">
@@ -20959,15 +20953,15 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A59" s="301" t="s">
+      <c r="A59" s="333" t="s">
         <v>1129</v>
       </c>
-      <c r="B59" s="302"/>
-      <c r="C59" s="302"/>
-      <c r="D59" s="302"/>
-      <c r="E59" s="302"/>
-      <c r="F59" s="302"/>
-      <c r="G59" s="303"/>
+      <c r="B59" s="334"/>
+      <c r="C59" s="334"/>
+      <c r="D59" s="334"/>
+      <c r="E59" s="334"/>
+      <c r="F59" s="334"/>
+      <c r="G59" s="335"/>
     </row>
     <row r="60" spans="1:7" ht="38.25">
       <c r="A60" s="83" t="s">
@@ -21453,15 +21447,15 @@
       </c>
     </row>
     <row r="81" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A81" s="301" t="s">
+      <c r="A81" s="333" t="s">
         <v>1140</v>
       </c>
-      <c r="B81" s="302"/>
-      <c r="C81" s="302"/>
-      <c r="D81" s="302"/>
-      <c r="E81" s="302"/>
-      <c r="F81" s="302"/>
-      <c r="G81" s="303"/>
+      <c r="B81" s="334"/>
+      <c r="C81" s="334"/>
+      <c r="D81" s="334"/>
+      <c r="E81" s="334"/>
+      <c r="F81" s="334"/>
+      <c r="G81" s="335"/>
     </row>
     <row r="82" spans="1:7" ht="38.25">
       <c r="A82" s="83" t="s">
@@ -21947,26 +21941,26 @@
       </c>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="304" t="s">
-        <v>231</v>
-      </c>
-      <c r="B103" s="305"/>
-      <c r="C103" s="305"/>
-      <c r="D103" s="305"/>
-      <c r="E103" s="305"/>
-      <c r="F103" s="305"/>
-      <c r="G103" s="306"/>
+      <c r="A103" s="336" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" s="337"/>
+      <c r="C103" s="337"/>
+      <c r="D103" s="337"/>
+      <c r="E103" s="337"/>
+      <c r="F103" s="337"/>
+      <c r="G103" s="338"/>
     </row>
     <row r="104" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A104" s="295" t="s">
+      <c r="A104" s="327" t="s">
         <v>1143</v>
       </c>
-      <c r="B104" s="296"/>
-      <c r="C104" s="296"/>
-      <c r="D104" s="296"/>
-      <c r="E104" s="296"/>
-      <c r="F104" s="296"/>
-      <c r="G104" s="297"/>
+      <c r="B104" s="328"/>
+      <c r="C104" s="328"/>
+      <c r="D104" s="328"/>
+      <c r="E104" s="328"/>
+      <c r="F104" s="328"/>
+      <c r="G104" s="329"/>
     </row>
     <row r="105" spans="1:7" ht="63">
       <c r="A105" s="87" t="s">
@@ -21992,15 +21986,15 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A106" s="295" t="s">
+      <c r="A106" s="327" t="s">
         <v>1148</v>
       </c>
-      <c r="B106" s="296"/>
-      <c r="C106" s="296"/>
-      <c r="D106" s="296"/>
-      <c r="E106" s="296"/>
-      <c r="F106" s="296"/>
-      <c r="G106" s="297"/>
+      <c r="B106" s="328"/>
+      <c r="C106" s="328"/>
+      <c r="D106" s="328"/>
+      <c r="E106" s="328"/>
+      <c r="F106" s="328"/>
+      <c r="G106" s="329"/>
     </row>
     <row r="107" spans="1:7" ht="63">
       <c r="A107" s="87" t="s">
@@ -22026,15 +22020,15 @@
       </c>
     </row>
     <row r="108" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A108" s="295" t="s">
+      <c r="A108" s="327" t="s">
         <v>1151</v>
       </c>
-      <c r="B108" s="296"/>
-      <c r="C108" s="296"/>
-      <c r="D108" s="296"/>
-      <c r="E108" s="296"/>
-      <c r="F108" s="296"/>
-      <c r="G108" s="297"/>
+      <c r="B108" s="328"/>
+      <c r="C108" s="328"/>
+      <c r="D108" s="328"/>
+      <c r="E108" s="328"/>
+      <c r="F108" s="328"/>
+      <c r="G108" s="329"/>
     </row>
     <row r="109" spans="1:7" ht="38.25">
       <c r="A109" s="87" t="s">
@@ -22060,15 +22054,15 @@
       </c>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="295" t="s">
+      <c r="A110" s="327" t="s">
         <v>1155</v>
       </c>
-      <c r="B110" s="296"/>
-      <c r="C110" s="296"/>
-      <c r="D110" s="296"/>
-      <c r="E110" s="296"/>
-      <c r="F110" s="296"/>
-      <c r="G110" s="297"/>
+      <c r="B110" s="328"/>
+      <c r="C110" s="328"/>
+      <c r="D110" s="328"/>
+      <c r="E110" s="328"/>
+      <c r="F110" s="328"/>
+      <c r="G110" s="329"/>
     </row>
     <row r="111" spans="1:7" ht="50.25">
       <c r="A111" s="87" t="s">
@@ -22094,15 +22088,15 @@
       </c>
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1">
-      <c r="A112" s="295" t="s">
+      <c r="A112" s="327" t="s">
         <v>1159</v>
       </c>
-      <c r="B112" s="296"/>
-      <c r="C112" s="296"/>
-      <c r="D112" s="296"/>
-      <c r="E112" s="296"/>
-      <c r="F112" s="296"/>
-      <c r="G112" s="297"/>
+      <c r="B112" s="328"/>
+      <c r="C112" s="328"/>
+      <c r="D112" s="328"/>
+      <c r="E112" s="328"/>
+      <c r="F112" s="328"/>
+      <c r="G112" s="329"/>
     </row>
     <row r="113" spans="1:7" ht="75.75">
       <c r="A113" s="87" t="s">
@@ -22129,12 +22123,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A108:G108"/>
     <mergeCell ref="A110:G110"/>
@@ -22145,6 +22133,12 @@
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A103:G103"/>
     <mergeCell ref="A104:G104"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22166,36 +22160,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="340" t="s">
         <v>1163</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
+      <c r="B1" s="340"/>
+      <c r="C1" s="340"/>
+      <c r="D1" s="340"/>
+      <c r="E1" s="340"/>
+      <c r="F1" s="340"/>
       <c r="G1" s="89"/>
     </row>
     <row r="2" spans="1:7" ht="42" customHeight="1">
-      <c r="A2" s="325" t="s">
+      <c r="A2" s="341" t="s">
         <v>1164</v>
       </c>
-      <c r="B2" s="325"/>
-      <c r="C2" s="325"/>
-      <c r="D2" s="325"/>
-      <c r="E2" s="325"/>
-      <c r="F2" s="325"/>
+      <c r="B2" s="341"/>
+      <c r="C2" s="341"/>
+      <c r="D2" s="341"/>
+      <c r="E2" s="341"/>
+      <c r="F2" s="341"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A3" s="326" t="s">
+      <c r="A3" s="342" t="s">
         <v>1165</v>
       </c>
-      <c r="B3" s="326"/>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="326"/>
-      <c r="F3" s="326"/>
+      <c r="B3" s="342"/>
+      <c r="C3" s="342"/>
+      <c r="D3" s="342"/>
+      <c r="E3" s="342"/>
+      <c r="F3" s="342"/>
       <c r="G3" s="89"/>
     </row>
     <row r="4" spans="1:7" ht="22.5" customHeight="1">
@@ -22211,10 +22205,10 @@
       <c r="D4" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="327" t="s">
+      <c r="E4" s="343" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="328"/>
+      <c r="F4" s="344"/>
     </row>
     <row r="5" spans="1:7" ht="54" customHeight="1">
       <c r="A5" s="152">
@@ -22229,10 +22223,10 @@
       <c r="D5" s="104" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="329" t="s">
+      <c r="E5" s="345" t="s">
         <v>1168</v>
       </c>
-      <c r="F5" s="330"/>
+      <c r="F5" s="346"/>
     </row>
     <row r="6" spans="1:7" ht="39" customHeight="1">
       <c r="A6" s="153">
@@ -22247,10 +22241,10 @@
       <c r="D6" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="329" t="s">
+      <c r="E6" s="345" t="s">
         <v>1170</v>
       </c>
-      <c r="F6" s="330"/>
+      <c r="F6" s="346"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="89"/>
@@ -22262,15 +22256,15 @@
       <c r="G7" s="89"/>
     </row>
     <row r="8" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A8" s="323" t="s">
+      <c r="A8" s="339" t="s">
         <v>1171</v>
       </c>
-      <c r="B8" s="323"/>
-      <c r="C8" s="323"/>
-      <c r="D8" s="323"/>
-      <c r="E8" s="323"/>
-      <c r="F8" s="323"/>
-      <c r="G8" s="323"/>
+      <c r="B8" s="339"/>
+      <c r="C8" s="339"/>
+      <c r="D8" s="339"/>
+      <c r="E8" s="339"/>
+      <c r="F8" s="339"/>
+      <c r="G8" s="339"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="98" t="s">
@@ -22670,37 +22664,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="333" t="s">
+      <c r="A1" s="349" t="s">
         <v>1200</v>
       </c>
-      <c r="B1" s="333"/>
-      <c r="C1" s="333"/>
-      <c r="D1" s="333"/>
-      <c r="E1" s="333"/>
-      <c r="F1" s="333"/>
-      <c r="G1" s="333"/>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
     </row>
     <row r="2" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A2" s="334" t="s">
+      <c r="A2" s="350" t="s">
         <v>1201</v>
       </c>
-      <c r="B2" s="334"/>
-      <c r="C2" s="334"/>
-      <c r="D2" s="334"/>
-      <c r="E2" s="334"/>
-      <c r="F2" s="334"/>
-      <c r="G2" s="334"/>
+      <c r="B2" s="350"/>
+      <c r="C2" s="350"/>
+      <c r="D2" s="350"/>
+      <c r="E2" s="350"/>
+      <c r="F2" s="350"/>
+      <c r="G2" s="350"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="333" t="s">
+      <c r="A3" s="349" t="s">
         <v>1202</v>
       </c>
-      <c r="B3" s="333"/>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333"/>
-      <c r="G3" s="333"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="111" t="s">
@@ -22715,11 +22709,11 @@
       <c r="D4" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="335" t="s">
+      <c r="E4" s="351" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="336"/>
-      <c r="G4" s="337"/>
+      <c r="F4" s="352"/>
+      <c r="G4" s="353"/>
     </row>
     <row r="5" spans="1:7" ht="48.75" customHeight="1">
       <c r="A5" s="113">
@@ -22734,11 +22728,11 @@
       <c r="D5" s="114" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="331" t="s">
+      <c r="E5" s="347" t="s">
         <v>1204</v>
       </c>
-      <c r="F5" s="331"/>
-      <c r="G5" s="332"/>
+      <c r="F5" s="347"/>
+      <c r="G5" s="348"/>
     </row>
     <row r="6" spans="1:7" ht="85.5" customHeight="1">
       <c r="A6" s="116">
@@ -22753,11 +22747,11 @@
       <c r="D6" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="331" t="s">
+      <c r="E6" s="347" t="s">
         <v>1207</v>
       </c>
-      <c r="F6" s="331"/>
-      <c r="G6" s="332"/>
+      <c r="F6" s="347"/>
+      <c r="G6" s="348"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="122"/>
@@ -22769,15 +22763,15 @@
       <c r="G7" s="122"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
-      <c r="A8" s="333" t="s">
+      <c r="A8" s="349" t="s">
         <v>1208</v>
       </c>
-      <c r="B8" s="333"/>
-      <c r="C8" s="333"/>
-      <c r="D8" s="333"/>
-      <c r="E8" s="333"/>
-      <c r="F8" s="333"/>
-      <c r="G8" s="333"/>
+      <c r="B8" s="349"/>
+      <c r="C8" s="349"/>
+      <c r="D8" s="349"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
+      <c r="G8" s="349"/>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1">
       <c r="A9" s="111" t="s">
@@ -23199,37 +23193,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1231</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A2" s="339" t="s">
+      <c r="A2" s="355" t="s">
         <v>1232</v>
       </c>
-      <c r="B2" s="339"/>
-      <c r="C2" s="339"/>
-      <c r="D2" s="339"/>
-      <c r="E2" s="339"/>
-      <c r="F2" s="339"/>
-      <c r="G2" s="339"/>
+      <c r="B2" s="355"/>
+      <c r="C2" s="355"/>
+      <c r="D2" s="355"/>
+      <c r="E2" s="355"/>
+      <c r="F2" s="355"/>
+      <c r="G2" s="355"/>
     </row>
     <row r="3" spans="1:7" ht="23.25" customHeight="1">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1233</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1">
       <c r="A4" s="102" t="s">
@@ -23244,11 +23238,11 @@
       <c r="D4" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="340" t="s">
+      <c r="E4" s="356" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="340"/>
-      <c r="G4" s="341"/>
+      <c r="F4" s="356"/>
+      <c r="G4" s="357"/>
     </row>
     <row r="5" spans="1:7" ht="62.25" customHeight="1">
       <c r="A5" s="104">
@@ -23263,11 +23257,11 @@
       <c r="D5" s="105" t="s">
         <v>1235</v>
       </c>
-      <c r="E5" s="329" t="s">
+      <c r="E5" s="345" t="s">
         <v>1236</v>
       </c>
-      <c r="F5" s="329"/>
-      <c r="G5" s="330"/>
+      <c r="F5" s="345"/>
+      <c r="G5" s="346"/>
     </row>
     <row r="6" spans="1:7" ht="49.5" customHeight="1">
       <c r="A6" s="106">
@@ -23282,11 +23276,11 @@
       <c r="D6" s="107" t="s">
         <v>1239</v>
       </c>
-      <c r="E6" s="329" t="s">
+      <c r="E6" s="345" t="s">
         <v>1240</v>
       </c>
-      <c r="F6" s="329"/>
-      <c r="G6" s="330"/>
+      <c r="F6" s="345"/>
+      <c r="G6" s="346"/>
     </row>
     <row r="7" spans="1:7" ht="49.5" customHeight="1">
       <c r="A7" s="106">
@@ -23301,11 +23295,11 @@
       <c r="D7" s="107" t="s">
         <v>1243</v>
       </c>
-      <c r="E7" s="329" t="s">
+      <c r="E7" s="345" t="s">
         <v>1244</v>
       </c>
-      <c r="F7" s="329"/>
-      <c r="G7" s="330"/>
+      <c r="F7" s="345"/>
+      <c r="G7" s="346"/>
     </row>
     <row r="8" spans="1:7" ht="15">
       <c r="A8" s="100"/>
@@ -23317,15 +23311,15 @@
       <c r="G8" s="100"/>
     </row>
     <row r="9" spans="1:7" ht="23.25" customHeight="1">
-      <c r="A9" s="338" t="s">
+      <c r="A9" s="354" t="s">
         <v>1245</v>
       </c>
-      <c r="B9" s="338"/>
-      <c r="C9" s="338"/>
-      <c r="D9" s="338"/>
-      <c r="E9" s="338"/>
-      <c r="F9" s="338"/>
-      <c r="G9" s="338"/>
+      <c r="B9" s="354"/>
+      <c r="C9" s="354"/>
+      <c r="D9" s="354"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
+      <c r="G9" s="354"/>
     </row>
     <row r="10" spans="1:7" ht="21.75" customHeight="1">
       <c r="A10" s="125" t="s">
@@ -23351,15 +23345,15 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A11" s="338" t="s">
+      <c r="A11" s="354" t="s">
         <v>1247</v>
       </c>
-      <c r="B11" s="338"/>
-      <c r="C11" s="338"/>
-      <c r="D11" s="338"/>
-      <c r="E11" s="338"/>
-      <c r="F11" s="338"/>
-      <c r="G11" s="338"/>
+      <c r="B11" s="354"/>
+      <c r="C11" s="354"/>
+      <c r="D11" s="354"/>
+      <c r="E11" s="354"/>
+      <c r="F11" s="354"/>
+      <c r="G11" s="354"/>
     </row>
     <row r="12" spans="1:7" ht="125.25" customHeight="1">
       <c r="A12" s="104">
@@ -23845,15 +23839,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A33" s="342" t="s">
+      <c r="A33" s="358" t="s">
         <v>1278</v>
       </c>
-      <c r="B33" s="343"/>
-      <c r="C33" s="343"/>
-      <c r="D33" s="343"/>
-      <c r="E33" s="343"/>
-      <c r="F33" s="343"/>
-      <c r="G33" s="344"/>
+      <c r="B33" s="359"/>
+      <c r="C33" s="359"/>
+      <c r="D33" s="359"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
+      <c r="G33" s="360"/>
     </row>
     <row r="34" spans="1:7" ht="104.25" customHeight="1">
       <c r="A34" s="106">
@@ -24339,15 +24333,15 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="24" customHeight="1">
-      <c r="A55" s="338" t="s">
+      <c r="A55" s="354" t="s">
         <v>1291</v>
       </c>
-      <c r="B55" s="338"/>
-      <c r="C55" s="338"/>
-      <c r="D55" s="338"/>
-      <c r="E55" s="338"/>
-      <c r="F55" s="338"/>
-      <c r="G55" s="338"/>
+      <c r="B55" s="354"/>
+      <c r="C55" s="354"/>
+      <c r="D55" s="354"/>
+      <c r="E55" s="354"/>
+      <c r="F55" s="354"/>
+      <c r="G55" s="354"/>
     </row>
     <row r="56" spans="1:7" ht="101.25">
       <c r="A56" s="104">
@@ -24833,15 +24827,15 @@
       </c>
     </row>
     <row r="77" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A77" s="338" t="s">
+      <c r="A77" s="354" t="s">
         <v>1295</v>
       </c>
-      <c r="B77" s="338"/>
-      <c r="C77" s="338"/>
-      <c r="D77" s="338"/>
-      <c r="E77" s="338"/>
-      <c r="F77" s="338"/>
-      <c r="G77" s="338"/>
+      <c r="B77" s="354"/>
+      <c r="C77" s="354"/>
+      <c r="D77" s="354"/>
+      <c r="E77" s="354"/>
+      <c r="F77" s="354"/>
+      <c r="G77" s="354"/>
     </row>
     <row r="78" spans="1:7" ht="113.25" customHeight="1">
       <c r="A78" s="104">
@@ -25361,31 +25355,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="347" t="s">
+      <c r="A1" s="363" t="s">
         <v>1300</v>
       </c>
-      <c r="B1" s="348"/>
-      <c r="C1" s="348"/>
-      <c r="D1" s="348"/>
-      <c r="E1" s="349"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="364"/>
+      <c r="D1" s="364"/>
+      <c r="E1" s="365"/>
     </row>
     <row r="2" spans="1:5" ht="23.25" customHeight="1">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="366" t="s">
         <v>1301</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
     </row>
     <row r="3" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A3" s="347" t="s">
+      <c r="A3" s="363" t="s">
         <v>1302</v>
       </c>
-      <c r="B3" s="348"/>
-      <c r="C3" s="348"/>
-      <c r="D3" s="348"/>
-      <c r="E3" s="349"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="365"/>
     </row>
     <row r="4" spans="1:5" ht="19.5" customHeight="1">
       <c r="A4" s="143" t="s">
@@ -25394,10 +25388,10 @@
       <c r="B4" s="144" t="s">
         <v>1303</v>
       </c>
-      <c r="C4" s="348" t="s">
+      <c r="C4" s="364" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="349"/>
+      <c r="D4" s="365"/>
       <c r="E4" s="144" t="s">
         <v>1304</v>
       </c>
@@ -25409,10 +25403,10 @@
       <c r="B5" s="132" t="s">
         <v>1305</v>
       </c>
-      <c r="C5" s="345" t="s">
+      <c r="C5" s="361" t="s">
         <v>1306</v>
       </c>
-      <c r="D5" s="346"/>
+      <c r="D5" s="362"/>
       <c r="E5" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25424,10 +25418,10 @@
       <c r="B6" s="132" t="s">
         <v>1308</v>
       </c>
-      <c r="C6" s="345" t="s">
+      <c r="C6" s="361" t="s">
         <v>1309</v>
       </c>
-      <c r="D6" s="346"/>
+      <c r="D6" s="362"/>
       <c r="E6" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25439,10 +25433,10 @@
       <c r="B7" s="132" t="s">
         <v>1310</v>
       </c>
-      <c r="C7" s="345" t="s">
+      <c r="C7" s="361" t="s">
         <v>1311</v>
       </c>
-      <c r="D7" s="346"/>
+      <c r="D7" s="362"/>
       <c r="E7" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25454,10 +25448,10 @@
       <c r="B8" s="132" t="s">
         <v>1312</v>
       </c>
-      <c r="C8" s="345" t="s">
+      <c r="C8" s="361" t="s">
         <v>1313</v>
       </c>
-      <c r="D8" s="346"/>
+      <c r="D8" s="362"/>
       <c r="E8" s="132" t="s">
         <v>178</v>
       </c>
@@ -25469,10 +25463,10 @@
       <c r="B9" s="132" t="s">
         <v>1314</v>
       </c>
-      <c r="C9" s="345" t="s">
+      <c r="C9" s="361" t="s">
         <v>1315</v>
       </c>
-      <c r="D9" s="346"/>
+      <c r="D9" s="362"/>
       <c r="E9" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25484,10 +25478,10 @@
       <c r="B10" s="132" t="s">
         <v>1316</v>
       </c>
-      <c r="C10" s="345" t="s">
+      <c r="C10" s="361" t="s">
         <v>1317</v>
       </c>
-      <c r="D10" s="346"/>
+      <c r="D10" s="362"/>
       <c r="E10" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25499,10 +25493,10 @@
       <c r="B11" s="132" t="s">
         <v>1318</v>
       </c>
-      <c r="C11" s="345" t="s">
+      <c r="C11" s="361" t="s">
         <v>1319</v>
       </c>
-      <c r="D11" s="346"/>
+      <c r="D11" s="362"/>
       <c r="E11" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25514,10 +25508,10 @@
       <c r="B12" s="132" t="s">
         <v>1320</v>
       </c>
-      <c r="C12" s="345" t="s">
+      <c r="C12" s="361" t="s">
         <v>1321</v>
       </c>
-      <c r="D12" s="346"/>
+      <c r="D12" s="362"/>
       <c r="E12" s="132" t="s">
         <v>1322</v>
       </c>
@@ -25529,10 +25523,10 @@
       <c r="B13" s="159" t="s">
         <v>1323</v>
       </c>
-      <c r="C13" s="345" t="s">
+      <c r="C13" s="361" t="s">
         <v>1324</v>
       </c>
-      <c r="D13" s="346"/>
+      <c r="D13" s="362"/>
       <c r="E13" s="132" t="s">
         <v>1325</v>
       </c>
@@ -25544,10 +25538,10 @@
       <c r="B14" s="132" t="s">
         <v>1326</v>
       </c>
-      <c r="C14" s="345" t="s">
+      <c r="C14" s="361" t="s">
         <v>1327</v>
       </c>
-      <c r="D14" s="346"/>
+      <c r="D14" s="362"/>
       <c r="E14" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25600,10 +25594,10 @@
       <c r="B18" s="159" t="s">
         <v>1337</v>
       </c>
-      <c r="C18" s="345" t="s">
+      <c r="C18" s="361" t="s">
         <v>1338</v>
       </c>
-      <c r="D18" s="346"/>
+      <c r="D18" s="362"/>
       <c r="E18" s="132" t="s">
         <v>1339</v>
       </c>
@@ -25615,10 +25609,10 @@
       <c r="B19" s="132" t="s">
         <v>1340</v>
       </c>
-      <c r="C19" s="345" t="s">
+      <c r="C19" s="361" t="s">
         <v>1341</v>
       </c>
-      <c r="D19" s="346"/>
+      <c r="D19" s="362"/>
       <c r="E19" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25630,10 +25624,10 @@
       <c r="B20" s="132" t="s">
         <v>1342</v>
       </c>
-      <c r="C20" s="345" t="s">
+      <c r="C20" s="361" t="s">
         <v>1343</v>
       </c>
-      <c r="D20" s="346"/>
+      <c r="D20" s="362"/>
       <c r="E20" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25645,10 +25639,10 @@
       <c r="B21" s="132" t="s">
         <v>1344</v>
       </c>
-      <c r="C21" s="345" t="s">
+      <c r="C21" s="361" t="s">
         <v>1345</v>
       </c>
-      <c r="D21" s="346"/>
+      <c r="D21" s="362"/>
       <c r="E21" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25660,10 +25654,10 @@
       <c r="B22" s="132" t="s">
         <v>1346</v>
       </c>
-      <c r="C22" s="345" t="s">
+      <c r="C22" s="361" t="s">
         <v>1347</v>
       </c>
-      <c r="D22" s="346"/>
+      <c r="D22" s="362"/>
       <c r="E22" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25675,10 +25669,10 @@
       <c r="B23" s="132" t="s">
         <v>1348</v>
       </c>
-      <c r="C23" s="345" t="s">
+      <c r="C23" s="361" t="s">
         <v>1349</v>
       </c>
-      <c r="D23" s="346"/>
+      <c r="D23" s="362"/>
       <c r="E23" s="132" t="s">
         <v>1307</v>
       </c>
@@ -25690,10 +25684,10 @@
       <c r="B24" s="132" t="s">
         <v>1350</v>
       </c>
-      <c r="C24" s="345" t="s">
+      <c r="C24" s="361" t="s">
         <v>1351</v>
       </c>
-      <c r="D24" s="346"/>
+      <c r="D24" s="362"/>
       <c r="E24" s="132" t="s">
         <v>1352</v>
       </c>
@@ -25705,10 +25699,10 @@
       <c r="B25" s="132" t="s">
         <v>1353</v>
       </c>
-      <c r="C25" s="345" t="s">
-        <v>231</v>
-      </c>
-      <c r="D25" s="346"/>
+      <c r="C25" s="361" t="s">
+        <v>231</v>
+      </c>
+      <c r="D25" s="362"/>
       <c r="E25" s="132" t="s">
         <v>1354</v>
       </c>
@@ -25721,13 +25715,13 @@
       <c r="E26" s="100"/>
     </row>
     <row r="27" spans="1:5" ht="23.25" customHeight="1">
-      <c r="A27" s="347" t="s">
+      <c r="A27" s="363" t="s">
         <v>1355</v>
       </c>
-      <c r="B27" s="348"/>
-      <c r="C27" s="348"/>
-      <c r="D27" s="348"/>
-      <c r="E27" s="349"/>
+      <c r="B27" s="364"/>
+      <c r="C27" s="364"/>
+      <c r="D27" s="364"/>
+      <c r="E27" s="365"/>
     </row>
     <row r="28" spans="1:5" ht="26.25" customHeight="1">
       <c r="A28" s="143" t="s">
@@ -25933,11 +25927,12 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
@@ -25950,12 +25945,11 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25979,37 +25973,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A1" s="333" t="s">
+      <c r="A1" s="349" t="s">
         <v>1376</v>
       </c>
-      <c r="B1" s="333"/>
-      <c r="C1" s="333"/>
-      <c r="D1" s="333"/>
-      <c r="E1" s="333"/>
-      <c r="F1" s="333"/>
-      <c r="G1" s="333"/>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
     </row>
     <row r="2" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A2" s="334" t="s">
+      <c r="A2" s="350" t="s">
         <v>1377</v>
       </c>
-      <c r="B2" s="334"/>
-      <c r="C2" s="334"/>
-      <c r="D2" s="334"/>
-      <c r="E2" s="334"/>
-      <c r="F2" s="334"/>
-      <c r="G2" s="334"/>
+      <c r="B2" s="350"/>
+      <c r="C2" s="350"/>
+      <c r="D2" s="350"/>
+      <c r="E2" s="350"/>
+      <c r="F2" s="350"/>
+      <c r="G2" s="350"/>
     </row>
     <row r="3" spans="1:7" ht="39.75" customHeight="1">
-      <c r="A3" s="333" t="s">
+      <c r="A3" s="349" t="s">
         <v>1302</v>
       </c>
-      <c r="B3" s="333"/>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333"/>
-      <c r="G3" s="333"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" s="123" t="s">
@@ -26024,11 +26018,11 @@
       <c r="D4" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="351" t="s">
+      <c r="E4" s="367" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="352"/>
-      <c r="G4" s="353"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="369"/>
     </row>
     <row r="5" spans="1:7" ht="186" customHeight="1">
       <c r="A5" s="131">
@@ -26043,11 +26037,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>1380</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" s="100"/>
@@ -26059,15 +26053,15 @@
       <c r="G6" s="100"/>
     </row>
     <row r="7" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A7" s="338" t="s">
+      <c r="A7" s="354" t="s">
         <v>1355</v>
       </c>
-      <c r="B7" s="338"/>
-      <c r="C7" s="338"/>
-      <c r="D7" s="338"/>
-      <c r="E7" s="338"/>
-      <c r="F7" s="338"/>
-      <c r="G7" s="338"/>
+      <c r="B7" s="354"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
+      <c r="G7" s="354"/>
     </row>
     <row r="8" spans="1:7" ht="25.5" customHeight="1">
       <c r="A8" s="125" t="s">
@@ -26402,7 +26396,7 @@
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="445" t="s">
         <v>21</v>
       </c>
     </row>
@@ -26429,42 +26423,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="314" t="s">
         <v>1395</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="357"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="373"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1">
-      <c r="A2" s="358"/>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="360"/>
+      <c r="A2" s="374"/>
+      <c r="B2" s="375"/>
+      <c r="C2" s="375"/>
+      <c r="D2" s="375"/>
+      <c r="E2" s="375"/>
+      <c r="F2" s="376"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1043</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="338" t="s">
+      <c r="A4" s="354" t="s">
         <v>1044</v>
       </c>
-      <c r="B4" s="338"/>
-      <c r="C4" s="338"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="338"/>
+      <c r="B4" s="354"/>
+      <c r="C4" s="354"/>
+      <c r="D4" s="354"/>
+      <c r="E4" s="354"/>
+      <c r="F4" s="354"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="80" t="s">
@@ -26607,24 +26601,24 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="32.450000000000003" customHeight="1">
-      <c r="A12" s="320" t="s">
-        <v>231</v>
-      </c>
-      <c r="B12" s="321"/>
-      <c r="C12" s="321"/>
-      <c r="D12" s="321"/>
-      <c r="E12" s="321"/>
-      <c r="F12" s="361"/>
+      <c r="A12" s="324" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="325"/>
+      <c r="C12" s="325"/>
+      <c r="D12" s="325"/>
+      <c r="E12" s="325"/>
+      <c r="F12" s="377"/>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="307" t="s">
+      <c r="A13" s="311" t="s">
         <v>1067</v>
       </c>
-      <c r="B13" s="308"/>
-      <c r="C13" s="308"/>
-      <c r="D13" s="308"/>
-      <c r="E13" s="308"/>
-      <c r="F13" s="356"/>
+      <c r="B13" s="312"/>
+      <c r="C13" s="312"/>
+      <c r="D13" s="312"/>
+      <c r="E13" s="312"/>
+      <c r="F13" s="372"/>
     </row>
     <row r="14" spans="1:6" ht="29.25">
       <c r="A14" s="80" t="s">
@@ -27277,42 +27271,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="314" t="s">
         <v>1493</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="357"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="373"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A2" s="358"/>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="360"/>
+      <c r="A2" s="374"/>
+      <c r="B2" s="375"/>
+      <c r="C2" s="375"/>
+      <c r="D2" s="375"/>
+      <c r="E2" s="375"/>
+      <c r="F2" s="376"/>
     </row>
     <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1043</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
     </row>
     <row r="4" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A4" s="338" t="s">
+      <c r="A4" s="354" t="s">
         <v>1044</v>
       </c>
-      <c r="B4" s="338"/>
-      <c r="C4" s="338"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="338"/>
+      <c r="B4" s="354"/>
+      <c r="C4" s="354"/>
+      <c r="D4" s="354"/>
+      <c r="E4" s="354"/>
+      <c r="F4" s="354"/>
     </row>
     <row r="5" spans="1:6" ht="14.45" customHeight="1">
       <c r="A5" s="80" t="s">
@@ -27355,24 +27349,24 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="362" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="363"/>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="364"/>
+      <c r="A7" s="378" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="379"/>
+      <c r="C7" s="379"/>
+      <c r="D7" s="379"/>
+      <c r="E7" s="379"/>
+      <c r="F7" s="380"/>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="338" t="s">
+      <c r="A8" s="354" t="s">
         <v>1067</v>
       </c>
-      <c r="B8" s="338"/>
-      <c r="C8" s="338"/>
-      <c r="D8" s="338"/>
-      <c r="E8" s="338"/>
-      <c r="F8" s="338"/>
+      <c r="B8" s="354"/>
+      <c r="C8" s="354"/>
+      <c r="D8" s="354"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
     </row>
     <row r="9" spans="1:6" ht="29.1" customHeight="1">
       <c r="A9" s="91" t="s">
@@ -27885,44 +27879,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="314" t="s">
         <v>1503</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="357"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="373"/>
     </row>
     <row r="2" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A2" s="358" t="s">
+      <c r="A2" s="374" t="s">
         <v>1504</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="360"/>
+      <c r="B2" s="375"/>
+      <c r="C2" s="375"/>
+      <c r="D2" s="375"/>
+      <c r="E2" s="375"/>
+      <c r="F2" s="376"/>
     </row>
     <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1043</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A4" s="338" t="s">
+      <c r="A4" s="354" t="s">
         <v>1044</v>
       </c>
-      <c r="B4" s="338"/>
-      <c r="C4" s="338"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="338"/>
+      <c r="B4" s="354"/>
+      <c r="C4" s="354"/>
+      <c r="D4" s="354"/>
+      <c r="E4" s="354"/>
+      <c r="F4" s="354"/>
     </row>
     <row r="5" spans="1:6" ht="14.45" customHeight="1">
       <c r="A5" s="80" t="s">
@@ -27985,24 +27979,24 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="320" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="321"/>
-      <c r="C8" s="321"/>
-      <c r="D8" s="321"/>
-      <c r="E8" s="321"/>
-      <c r="F8" s="322"/>
+      <c r="A8" s="324" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="325"/>
+      <c r="C8" s="325"/>
+      <c r="D8" s="325"/>
+      <c r="E8" s="325"/>
+      <c r="F8" s="326"/>
     </row>
     <row r="9" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A9" s="338" t="s">
+      <c r="A9" s="354" t="s">
         <v>1067</v>
       </c>
-      <c r="B9" s="338"/>
-      <c r="C9" s="338"/>
-      <c r="D9" s="338"/>
-      <c r="E9" s="338"/>
-      <c r="F9" s="338"/>
+      <c r="B9" s="354"/>
+      <c r="C9" s="354"/>
+      <c r="D9" s="354"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
     </row>
     <row r="10" spans="1:6" ht="36.75" customHeight="1">
       <c r="A10" s="101" t="s">
@@ -28155,42 +28149,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="314" t="s">
         <v>1520</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="357"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="373"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A2" s="358"/>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="360"/>
+      <c r="A2" s="374"/>
+      <c r="B2" s="375"/>
+      <c r="C2" s="375"/>
+      <c r="D2" s="375"/>
+      <c r="E2" s="375"/>
+      <c r="F2" s="376"/>
     </row>
     <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1043</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
     </row>
     <row r="4" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A4" s="365" t="s">
+      <c r="A4" s="381" t="s">
         <v>1044</v>
       </c>
-      <c r="B4" s="365"/>
-      <c r="C4" s="365"/>
-      <c r="D4" s="365"/>
-      <c r="E4" s="365"/>
-      <c r="F4" s="365"/>
+      <c r="B4" s="381"/>
+      <c r="C4" s="381"/>
+      <c r="D4" s="381"/>
+      <c r="E4" s="381"/>
+      <c r="F4" s="381"/>
     </row>
     <row r="5" spans="1:6" ht="14.45" customHeight="1">
       <c r="A5" s="80" t="s">
@@ -28233,24 +28227,24 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="320" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="321"/>
-      <c r="C7" s="321"/>
-      <c r="D7" s="321"/>
-      <c r="E7" s="321"/>
-      <c r="F7" s="322"/>
+      <c r="A7" s="324" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="325"/>
+      <c r="C7" s="325"/>
+      <c r="D7" s="325"/>
+      <c r="E7" s="325"/>
+      <c r="F7" s="326"/>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="338" t="s">
+      <c r="A8" s="354" t="s">
         <v>1067</v>
       </c>
-      <c r="B8" s="338"/>
-      <c r="C8" s="338"/>
-      <c r="D8" s="338"/>
-      <c r="E8" s="338"/>
-      <c r="F8" s="338"/>
+      <c r="B8" s="354"/>
+      <c r="C8" s="354"/>
+      <c r="D8" s="354"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
     </row>
     <row r="9" spans="1:6" ht="43.5" customHeight="1">
       <c r="A9" s="128" t="s">
@@ -28501,45 +28495,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1544</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
       <c r="H1" s="100"/>
       <c r="I1" s="100"/>
       <c r="J1" s="100"/>
       <c r="K1" s="100"/>
     </row>
     <row r="2" spans="1:11" ht="27" customHeight="1">
-      <c r="A2" s="367" t="s">
+      <c r="A2" s="383" t="s">
         <v>1545</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
       <c r="H2" s="100"/>
       <c r="I2" s="100"/>
       <c r="J2" s="100"/>
       <c r="K2" s="100"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1546</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
       <c r="H3" s="100"/>
       <c r="I3" s="100"/>
       <c r="J3" s="100"/>
@@ -28560,11 +28554,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
       <c r="H4" s="100"/>
       <c r="I4" s="100"/>
       <c r="J4" s="100"/>
@@ -28583,11 +28577,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>1548</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
       <c r="H5" s="100"/>
       <c r="I5" s="100"/>
       <c r="J5" s="100"/>
@@ -28607,15 +28601,15 @@
       <c r="K6" s="100"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="338" t="s">
+      <c r="A7" s="354" t="s">
         <v>1549</v>
       </c>
-      <c r="B7" s="338"/>
-      <c r="C7" s="338"/>
-      <c r="D7" s="338"/>
-      <c r="E7" s="338"/>
-      <c r="F7" s="338"/>
-      <c r="G7" s="338"/>
+      <c r="B7" s="354"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
+      <c r="G7" s="354"/>
       <c r="H7" s="100"/>
       <c r="I7" s="100"/>
       <c r="J7" s="100"/>
@@ -28649,15 +28643,15 @@
       <c r="K8" s="100"/>
     </row>
     <row r="9" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A9" s="338" t="s">
+      <c r="A9" s="354" t="s">
         <v>1550</v>
       </c>
-      <c r="B9" s="338"/>
-      <c r="C9" s="338"/>
-      <c r="D9" s="338"/>
-      <c r="E9" s="338"/>
-      <c r="F9" s="338"/>
-      <c r="G9" s="338"/>
+      <c r="B9" s="354"/>
+      <c r="C9" s="354"/>
+      <c r="D9" s="354"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
+      <c r="G9" s="354"/>
       <c r="H9" s="100"/>
       <c r="I9" s="100"/>
       <c r="J9" s="100"/>
@@ -28988,15 +28982,15 @@
       <c r="K21" s="100"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A22" s="366" t="s">
+      <c r="A22" s="382" t="s">
         <v>1563</v>
       </c>
-      <c r="B22" s="366"/>
-      <c r="C22" s="366"/>
-      <c r="D22" s="366"/>
-      <c r="E22" s="366"/>
-      <c r="F22" s="366"/>
-      <c r="G22" s="366"/>
+      <c r="B22" s="382"/>
+      <c r="C22" s="382"/>
+      <c r="D22" s="382"/>
+      <c r="E22" s="382"/>
+      <c r="F22" s="382"/>
+      <c r="G22" s="382"/>
       <c r="H22" s="100"/>
       <c r="I22" s="100"/>
       <c r="J22" s="100"/>
@@ -29327,15 +29321,15 @@
       <c r="K34" s="100"/>
     </row>
     <row r="35" spans="1:11" ht="22.5" customHeight="1">
-      <c r="A35" s="366" t="s">
+      <c r="A35" s="382" t="s">
         <v>1567</v>
       </c>
-      <c r="B35" s="366"/>
-      <c r="C35" s="366"/>
-      <c r="D35" s="366"/>
-      <c r="E35" s="366"/>
-      <c r="F35" s="366"/>
-      <c r="G35" s="366"/>
+      <c r="B35" s="382"/>
+      <c r="C35" s="382"/>
+      <c r="D35" s="382"/>
+      <c r="E35" s="382"/>
+      <c r="F35" s="382"/>
+      <c r="G35" s="382"/>
       <c r="H35" s="100"/>
       <c r="I35" s="100"/>
       <c r="J35" s="100"/>
@@ -29666,15 +29660,15 @@
       <c r="K47" s="100"/>
     </row>
     <row r="48" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A48" s="338" t="s">
+      <c r="A48" s="354" t="s">
         <v>1571</v>
       </c>
-      <c r="B48" s="338"/>
-      <c r="C48" s="338"/>
-      <c r="D48" s="338"/>
-      <c r="E48" s="338"/>
-      <c r="F48" s="338"/>
-      <c r="G48" s="338"/>
+      <c r="B48" s="354"/>
+      <c r="C48" s="354"/>
+      <c r="D48" s="354"/>
+      <c r="E48" s="354"/>
+      <c r="F48" s="354"/>
+      <c r="G48" s="354"/>
       <c r="H48" s="100"/>
       <c r="I48" s="100"/>
       <c r="J48" s="100"/>
@@ -30005,15 +29999,15 @@
       <c r="K60" s="100"/>
     </row>
     <row r="61" spans="1:11" ht="27" customHeight="1">
-      <c r="A61" s="366" t="s">
+      <c r="A61" s="382" t="s">
         <v>1575</v>
       </c>
-      <c r="B61" s="366"/>
-      <c r="C61" s="366"/>
-      <c r="D61" s="366"/>
-      <c r="E61" s="366"/>
-      <c r="F61" s="366"/>
-      <c r="G61" s="366"/>
+      <c r="B61" s="382"/>
+      <c r="C61" s="382"/>
+      <c r="D61" s="382"/>
+      <c r="E61" s="382"/>
+      <c r="F61" s="382"/>
+      <c r="G61" s="382"/>
       <c r="H61" s="100"/>
       <c r="I61" s="100"/>
       <c r="J61" s="100"/>
@@ -30373,13 +30367,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="347" t="s">
+      <c r="A1" s="363" t="s">
         <v>1579</v>
       </c>
-      <c r="B1" s="348"/>
-      <c r="C1" s="348"/>
-      <c r="D1" s="348"/>
-      <c r="E1" s="349"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="364"/>
+      <c r="D1" s="364"/>
+      <c r="E1" s="365"/>
       <c r="F1" s="158"/>
       <c r="G1" s="158"/>
       <c r="H1" s="158"/>
@@ -30387,13 +30381,13 @@
       <c r="J1" s="158"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="366" t="s">
         <v>1580</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
       <c r="F2" s="158"/>
       <c r="G2" s="158"/>
       <c r="H2" s="158"/>
@@ -30401,13 +30395,13 @@
       <c r="J2" s="158"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="347" t="s">
+      <c r="A3" s="363" t="s">
         <v>1581</v>
       </c>
-      <c r="B3" s="348"/>
-      <c r="C3" s="348"/>
-      <c r="D3" s="348"/>
-      <c r="E3" s="349"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="365"/>
       <c r="F3" s="158"/>
       <c r="G3" s="158"/>
       <c r="H3" s="158"/>
@@ -30603,13 +30597,13 @@
       <c r="J12" s="158"/>
     </row>
     <row r="13" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A13" s="371" t="s">
+      <c r="A13" s="387" t="s">
         <v>1603</v>
       </c>
-      <c r="B13" s="372"/>
-      <c r="C13" s="372"/>
-      <c r="D13" s="372"/>
-      <c r="E13" s="373"/>
+      <c r="B13" s="388"/>
+      <c r="C13" s="388"/>
+      <c r="D13" s="388"/>
+      <c r="E13" s="389"/>
       <c r="F13" s="158"/>
       <c r="G13" s="158"/>
       <c r="H13" s="158"/>
@@ -30972,37 +30966,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1628</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A2" s="374" t="s">
+      <c r="A2" s="390" t="s">
         <v>1629</v>
       </c>
-      <c r="B2" s="374"/>
-      <c r="C2" s="374"/>
-      <c r="D2" s="374"/>
-      <c r="E2" s="374"/>
-      <c r="F2" s="374"/>
-      <c r="G2" s="374"/>
+      <c r="B2" s="390"/>
+      <c r="C2" s="390"/>
+      <c r="D2" s="390"/>
+      <c r="E2" s="390"/>
+      <c r="F2" s="390"/>
+      <c r="G2" s="390"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1581</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="125" t="s">
@@ -31017,11 +31011,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="167.25" customHeight="1">
       <c r="A5" s="131">
@@ -31036,11 +31030,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>1632</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="100"/>
@@ -31052,15 +31046,15 @@
       <c r="G6" s="100"/>
     </row>
     <row r="7" spans="1:7" ht="45.75" customHeight="1">
-      <c r="A7" s="338" t="s">
+      <c r="A7" s="354" t="s">
         <v>1603</v>
       </c>
-      <c r="B7" s="338"/>
-      <c r="C7" s="338"/>
-      <c r="D7" s="338"/>
-      <c r="E7" s="338"/>
-      <c r="F7" s="338"/>
-      <c r="G7" s="338"/>
+      <c r="B7" s="354"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
+      <c r="G7" s="354"/>
     </row>
     <row r="8" spans="1:7" ht="24.75" customHeight="1">
       <c r="A8" s="125" t="s">
@@ -31436,37 +31430,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1650</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="367" t="s">
+      <c r="A2" s="383" t="s">
         <v>1651</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1652</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
       <c r="A4" s="125" t="s">
@@ -31481,11 +31475,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1">
       <c r="A5" s="131">
@@ -31500,11 +31494,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>1653</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1">
       <c r="A6" s="131">
@@ -31519,11 +31513,11 @@
       <c r="D6" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="361" t="s">
         <v>1654</v>
       </c>
-      <c r="F6" s="345"/>
-      <c r="G6" s="346"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="362"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="100"/>
@@ -31535,15 +31529,15 @@
       <c r="G7" s="100"/>
     </row>
     <row r="8" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A8" s="338" t="s">
+      <c r="A8" s="354" t="s">
         <v>1655</v>
       </c>
-      <c r="B8" s="338"/>
-      <c r="C8" s="338"/>
-      <c r="D8" s="338"/>
-      <c r="E8" s="338"/>
-      <c r="F8" s="338"/>
-      <c r="G8" s="338"/>
+      <c r="B8" s="354"/>
+      <c r="C8" s="354"/>
+      <c r="D8" s="354"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
+      <c r="G8" s="354"/>
     </row>
     <row r="9" spans="1:7" ht="23.25" customHeight="1">
       <c r="A9" s="125" t="s">
@@ -32357,35 +32351,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1711</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
-      <c r="A2" s="367"/>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="A2" s="383"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1712</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="27" customHeight="1">
       <c r="A4" s="125" t="s">
@@ -32400,11 +32394,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="37.5" customHeight="1">
       <c r="A5" s="131">
@@ -32419,11 +32413,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>1714</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="91.5" customHeight="1">
       <c r="A6" s="131">
@@ -32438,11 +32432,11 @@
       <c r="D6" s="132" t="s">
         <v>1716</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="361" t="s">
         <v>1717</v>
       </c>
-      <c r="F6" s="345"/>
-      <c r="G6" s="346"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="362"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="142" t="s">
@@ -32468,15 +32462,15 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A8" s="338" t="s">
+      <c r="A8" s="354" t="s">
         <v>1718</v>
       </c>
-      <c r="B8" s="338"/>
-      <c r="C8" s="338"/>
-      <c r="D8" s="338"/>
-      <c r="E8" s="338"/>
-      <c r="F8" s="338"/>
-      <c r="G8" s="338"/>
+      <c r="B8" s="354"/>
+      <c r="C8" s="354"/>
+      <c r="D8" s="354"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
+      <c r="G8" s="354"/>
     </row>
     <row r="9" spans="1:7" ht="22.5" customHeight="1">
       <c r="A9" s="125" t="s">
@@ -33265,29 +33259,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33" customHeight="1">
-      <c r="A1" s="375" t="s">
+      <c r="A1" s="391" t="s">
         <v>1754</v>
       </c>
-      <c r="B1" s="376"/>
-      <c r="C1" s="376"/>
-      <c r="D1" s="376"/>
-      <c r="E1" s="377"/>
+      <c r="B1" s="392"/>
+      <c r="C1" s="392"/>
+      <c r="D1" s="392"/>
+      <c r="E1" s="393"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="378"/>
-      <c r="B2" s="379"/>
-      <c r="C2" s="379"/>
-      <c r="D2" s="379"/>
-      <c r="E2" s="379"/>
+      <c r="A2" s="394"/>
+      <c r="B2" s="395"/>
+      <c r="C2" s="395"/>
+      <c r="D2" s="395"/>
+      <c r="E2" s="395"/>
     </row>
     <row r="3" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A3" s="375" t="s">
+      <c r="A3" s="391" t="s">
         <v>1755</v>
       </c>
-      <c r="B3" s="376"/>
-      <c r="C3" s="376"/>
-      <c r="D3" s="376"/>
-      <c r="E3" s="377"/>
+      <c r="B3" s="392"/>
+      <c r="C3" s="392"/>
+      <c r="D3" s="392"/>
+      <c r="E3" s="393"/>
     </row>
     <row r="4" spans="1:5" ht="21.75" customHeight="1">
       <c r="A4" s="181" t="s">
@@ -33348,13 +33342,13 @@
       <c r="E7" s="100"/>
     </row>
     <row r="8" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A8" s="375" t="s">
+      <c r="A8" s="391" t="s">
         <v>1763</v>
       </c>
-      <c r="B8" s="376"/>
-      <c r="C8" s="376"/>
-      <c r="D8" s="376"/>
-      <c r="E8" s="377"/>
+      <c r="B8" s="392"/>
+      <c r="C8" s="392"/>
+      <c r="D8" s="392"/>
+      <c r="E8" s="393"/>
     </row>
     <row r="9" spans="1:5" ht="26.25" customHeight="1">
       <c r="A9" s="181" t="s">
@@ -33489,26 +33483,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="261" t="s">
+      <c r="A1" s="271" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="262"/>
-      <c r="C1" s="262"/>
-      <c r="D1" s="262"/>
-      <c r="E1" s="262"/>
-      <c r="F1" s="262"/>
-      <c r="G1" s="263"/>
+      <c r="B1" s="272"/>
+      <c r="C1" s="272"/>
+      <c r="D1" s="272"/>
+      <c r="E1" s="272"/>
+      <c r="F1" s="272"/>
+      <c r="G1" s="273"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="264" t="s">
+      <c r="A2" s="274" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="265"/>
-      <c r="C2" s="265"/>
-      <c r="D2" s="265"/>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="266"/>
+      <c r="B2" s="275"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
+      <c r="G2" s="276"/>
     </row>
     <row r="3" spans="1:7" ht="45.75" customHeight="1">
       <c r="A3" s="43" t="s">
@@ -33523,11 +33517,11 @@
       <c r="D3" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="258" t="s">
+      <c r="E3" s="268" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="259"/>
-      <c r="G3" s="260"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="270"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
       <c r="A4" s="28">
@@ -33542,11 +33536,11 @@
       <c r="D4" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="267" t="s">
+      <c r="E4" s="277" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="267"/>
-      <c r="G4" s="268"/>
+      <c r="F4" s="277"/>
+      <c r="G4" s="278"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="28">
@@ -33561,11 +33555,11 @@
       <c r="D5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="267" t="s">
+      <c r="E5" s="277" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="267"/>
-      <c r="G5" s="268"/>
+      <c r="F5" s="277"/>
+      <c r="G5" s="278"/>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="28">
@@ -33580,11 +33574,11 @@
       <c r="D6" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="267" t="s">
+      <c r="E6" s="277" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="267"/>
-      <c r="G6" s="268"/>
+      <c r="F6" s="277"/>
+      <c r="G6" s="278"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="28">
@@ -33599,22 +33593,22 @@
       <c r="D7" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="267" t="s">
+      <c r="E7" s="277" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="267"/>
-      <c r="G7" s="268"/>
+      <c r="F7" s="277"/>
+      <c r="G7" s="278"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="264" t="s">
+      <c r="A8" s="274" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="265"/>
-      <c r="C8" s="265"/>
-      <c r="D8" s="265"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="266"/>
+      <c r="B8" s="275"/>
+      <c r="C8" s="275"/>
+      <c r="D8" s="275"/>
+      <c r="E8" s="275"/>
+      <c r="F8" s="275"/>
+      <c r="G8" s="276"/>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1">
       <c r="A9" s="43" t="s">
@@ -33640,15 +33634,15 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="24" customHeight="1">
-      <c r="A10" s="255" t="s">
+      <c r="A10" s="265" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="256"/>
-      <c r="C10" s="256"/>
-      <c r="D10" s="256"/>
-      <c r="E10" s="256"/>
-      <c r="F10" s="256"/>
-      <c r="G10" s="257"/>
+      <c r="B10" s="266"/>
+      <c r="C10" s="266"/>
+      <c r="D10" s="266"/>
+      <c r="E10" s="266"/>
+      <c r="F10" s="266"/>
+      <c r="G10" s="267"/>
     </row>
     <row r="11" spans="1:7" ht="24" customHeight="1">
       <c r="A11" s="28">
@@ -34180,15 +34174,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="24" customHeight="1">
-      <c r="A34" s="255" t="s">
+      <c r="A34" s="265" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="256"/>
-      <c r="C34" s="256"/>
-      <c r="D34" s="256"/>
-      <c r="E34" s="256"/>
-      <c r="F34" s="256"/>
-      <c r="G34" s="257"/>
+      <c r="B34" s="266"/>
+      <c r="C34" s="266"/>
+      <c r="D34" s="266"/>
+      <c r="E34" s="266"/>
+      <c r="F34" s="266"/>
+      <c r="G34" s="267"/>
     </row>
     <row r="35" spans="1:7" ht="24" customHeight="1">
       <c r="A35" s="28">
@@ -34720,15 +34714,15 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="24" customHeight="1">
-      <c r="A58" s="255" t="s">
+      <c r="A58" s="265" t="s">
         <v>126</v>
       </c>
-      <c r="B58" s="256"/>
-      <c r="C58" s="256"/>
-      <c r="D58" s="256"/>
-      <c r="E58" s="256"/>
-      <c r="F58" s="256"/>
-      <c r="G58" s="257"/>
+      <c r="B58" s="266"/>
+      <c r="C58" s="266"/>
+      <c r="D58" s="266"/>
+      <c r="E58" s="266"/>
+      <c r="F58" s="266"/>
+      <c r="G58" s="267"/>
     </row>
     <row r="59" spans="1:7" ht="24" customHeight="1">
       <c r="A59" s="28">
@@ -35260,15 +35254,15 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="36.75" customHeight="1">
-      <c r="A82" s="255" t="s">
+      <c r="A82" s="265" t="s">
         <v>150</v>
       </c>
-      <c r="B82" s="256"/>
-      <c r="C82" s="256"/>
-      <c r="D82" s="256"/>
-      <c r="E82" s="256"/>
-      <c r="F82" s="256"/>
-      <c r="G82" s="257"/>
+      <c r="B82" s="266"/>
+      <c r="C82" s="266"/>
+      <c r="D82" s="266"/>
+      <c r="E82" s="266"/>
+      <c r="F82" s="266"/>
+      <c r="G82" s="267"/>
     </row>
     <row r="83" spans="1:7" ht="24" customHeight="1">
       <c r="A83" s="28">
@@ -35837,37 +35831,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="10.5" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1773</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A2" s="380" t="s">
+      <c r="A2" s="396" t="s">
         <v>1774</v>
       </c>
-      <c r="B2" s="381"/>
-      <c r="C2" s="381"/>
-      <c r="D2" s="381"/>
-      <c r="E2" s="381"/>
-      <c r="F2" s="381"/>
-      <c r="G2" s="382"/>
+      <c r="B2" s="397"/>
+      <c r="C2" s="397"/>
+      <c r="D2" s="397"/>
+      <c r="E2" s="397"/>
+      <c r="F2" s="397"/>
+      <c r="G2" s="398"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="368" t="s">
+      <c r="A3" s="384" t="s">
         <v>1755</v>
       </c>
-      <c r="B3" s="369"/>
-      <c r="C3" s="369"/>
-      <c r="D3" s="369"/>
-      <c r="E3" s="369"/>
-      <c r="F3" s="369"/>
-      <c r="G3" s="370"/>
+      <c r="B3" s="385"/>
+      <c r="C3" s="385"/>
+      <c r="D3" s="385"/>
+      <c r="E3" s="385"/>
+      <c r="F3" s="385"/>
+      <c r="G3" s="386"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="143" t="s">
@@ -35882,11 +35876,11 @@
       <c r="D4" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="383" t="s">
+      <c r="E4" s="399" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="383"/>
-      <c r="G4" s="384"/>
+      <c r="F4" s="399"/>
+      <c r="G4" s="400"/>
     </row>
     <row r="5" spans="1:7" ht="78" customHeight="1">
       <c r="A5" s="131">
@@ -35901,11 +35895,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="345" t="s">
+      <c r="E5" s="361" t="s">
         <v>1776</v>
       </c>
-      <c r="F5" s="345"/>
-      <c r="G5" s="346"/>
+      <c r="F5" s="361"/>
+      <c r="G5" s="362"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="100"/>
@@ -35917,15 +35911,15 @@
       <c r="G6" s="100"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="338" t="s">
+      <c r="A7" s="354" t="s">
         <v>1763</v>
       </c>
-      <c r="B7" s="338"/>
-      <c r="C7" s="338"/>
-      <c r="D7" s="338"/>
-      <c r="E7" s="338"/>
-      <c r="F7" s="338"/>
-      <c r="G7" s="338"/>
+      <c r="B7" s="354"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
+      <c r="G7" s="354"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="125" t="s">
@@ -36117,37 +36111,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1784</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="27" customHeight="1">
-      <c r="A2" s="367" t="s">
+      <c r="A2" s="383" t="s">
         <v>1785</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7" ht="15">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1786</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" s="125" t="s">
@@ -36162,11 +36156,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="91.5" customHeight="1">
       <c r="A5" s="131">
@@ -36181,11 +36175,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>1788</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="99.75" customHeight="1">
       <c r="A6" s="131">
@@ -36200,11 +36194,11 @@
       <c r="D6" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="361" t="s">
         <v>1790</v>
       </c>
-      <c r="F6" s="345"/>
-      <c r="G6" s="346"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="362"/>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" s="100"/>
@@ -36216,15 +36210,15 @@
       <c r="G7" s="100"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A8" s="338" t="s">
+      <c r="A8" s="354" t="s">
         <v>1791</v>
       </c>
-      <c r="B8" s="338"/>
-      <c r="C8" s="338"/>
-      <c r="D8" s="338"/>
-      <c r="E8" s="338"/>
-      <c r="F8" s="338"/>
-      <c r="G8" s="338"/>
+      <c r="B8" s="354"/>
+      <c r="C8" s="354"/>
+      <c r="D8" s="354"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
+      <c r="G8" s="354"/>
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" s="125" t="s">
@@ -38488,37 +38482,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.25" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>1949</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="41.25" customHeight="1">
-      <c r="A2" s="367" t="s">
+      <c r="A2" s="383" t="s">
         <v>1950</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7" ht="15">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1951</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" s="125" t="s">
@@ -38533,11 +38527,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="78.75" customHeight="1">
       <c r="A5" s="131">
@@ -38552,11 +38546,11 @@
       <c r="D5" s="132" t="s">
         <v>1953</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>1954</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="43.5" customHeight="1">
       <c r="A6" s="131">
@@ -38571,11 +38565,11 @@
       <c r="D6" s="132" t="s">
         <v>1957</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="361" t="s">
         <v>1958</v>
       </c>
-      <c r="F6" s="345"/>
-      <c r="G6" s="346"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="362"/>
     </row>
     <row r="7" spans="1:7" ht="40.5" customHeight="1">
       <c r="A7" s="131">
@@ -38590,11 +38584,11 @@
       <c r="D7" s="132" t="s">
         <v>1961</v>
       </c>
-      <c r="E7" s="345" t="s">
+      <c r="E7" s="361" t="s">
         <v>1962</v>
       </c>
-      <c r="F7" s="345"/>
-      <c r="G7" s="346"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="362"/>
     </row>
     <row r="8" spans="1:7" ht="57" customHeight="1">
       <c r="A8" s="131">
@@ -38609,11 +38603,11 @@
       <c r="D8" s="132" t="s">
         <v>1964</v>
       </c>
-      <c r="E8" s="345" t="s">
+      <c r="E8" s="361" t="s">
         <v>1965</v>
       </c>
-      <c r="F8" s="345"/>
-      <c r="G8" s="346"/>
+      <c r="F8" s="361"/>
+      <c r="G8" s="362"/>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1">
       <c r="A9" s="100"/>
@@ -38625,15 +38619,15 @@
       <c r="G9" s="100"/>
     </row>
     <row r="10" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A10" s="368" t="s">
+      <c r="A10" s="384" t="s">
         <v>1966</v>
       </c>
-      <c r="B10" s="369"/>
-      <c r="C10" s="369"/>
-      <c r="D10" s="369"/>
-      <c r="E10" s="369"/>
-      <c r="F10" s="369"/>
-      <c r="G10" s="370"/>
+      <c r="B10" s="385"/>
+      <c r="C10" s="385"/>
+      <c r="D10" s="385"/>
+      <c r="E10" s="385"/>
+      <c r="F10" s="385"/>
+      <c r="G10" s="386"/>
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" s="145" t="s">
@@ -40850,28 +40844,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="347" t="s">
+      <c r="A1" s="363" t="s">
         <v>2068</v>
       </c>
-      <c r="B1" s="348"/>
-      <c r="C1" s="348"/>
-      <c r="D1" s="349"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="364"/>
+      <c r="D1" s="365"/>
     </row>
     <row r="2" spans="1:4" ht="33.75" customHeight="1">
-      <c r="A2" s="378" t="s">
+      <c r="A2" s="394" t="s">
         <v>2069</v>
       </c>
-      <c r="B2" s="379"/>
-      <c r="C2" s="379"/>
-      <c r="D2" s="379"/>
+      <c r="B2" s="395"/>
+      <c r="C2" s="395"/>
+      <c r="D2" s="395"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="347" t="s">
+      <c r="A3" s="363" t="s">
         <v>2070</v>
       </c>
-      <c r="B3" s="348"/>
-      <c r="C3" s="348"/>
-      <c r="D3" s="349"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="365"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="143" t="s">
@@ -41062,12 +41056,12 @@
       <c r="D17" s="100"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="347" t="s">
+      <c r="A18" s="363" t="s">
         <v>2089</v>
       </c>
-      <c r="B18" s="348"/>
-      <c r="C18" s="348"/>
-      <c r="D18" s="349"/>
+      <c r="B18" s="364"/>
+      <c r="C18" s="364"/>
+      <c r="D18" s="365"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="143" t="s">
@@ -41266,44 +41260,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="314" t="s">
         <v>2105</v>
       </c>
-      <c r="B1" s="311"/>
-      <c r="C1" s="311"/>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="312"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="316"/>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1">
-      <c r="A2" s="358" t="s">
+      <c r="A2" s="374" t="s">
         <v>2106</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="385"/>
+      <c r="B2" s="375"/>
+      <c r="C2" s="375"/>
+      <c r="D2" s="375"/>
+      <c r="E2" s="375"/>
+      <c r="F2" s="401"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>1043</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="338" t="s">
+      <c r="A4" s="354" t="s">
         <v>1044</v>
       </c>
-      <c r="B4" s="338"/>
-      <c r="C4" s="338"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="338"/>
+      <c r="B4" s="354"/>
+      <c r="C4" s="354"/>
+      <c r="D4" s="354"/>
+      <c r="E4" s="354"/>
+      <c r="F4" s="354"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="80" t="s">
@@ -41366,24 +41360,24 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="304" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="305"/>
-      <c r="C8" s="305"/>
-      <c r="D8" s="305"/>
-      <c r="E8" s="305"/>
-      <c r="F8" s="306"/>
+      <c r="A8" s="336" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="337"/>
+      <c r="C8" s="337"/>
+      <c r="D8" s="337"/>
+      <c r="E8" s="337"/>
+      <c r="F8" s="338"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="368" t="s">
+      <c r="A9" s="384" t="s">
         <v>1067</v>
       </c>
-      <c r="B9" s="369"/>
-      <c r="C9" s="369"/>
-      <c r="D9" s="369"/>
-      <c r="E9" s="369"/>
-      <c r="F9" s="370"/>
+      <c r="B9" s="385"/>
+      <c r="C9" s="385"/>
+      <c r="D9" s="385"/>
+      <c r="E9" s="385"/>
+      <c r="F9" s="386"/>
     </row>
     <row r="10" spans="1:6" ht="43.5">
       <c r="A10" s="145" t="s">
@@ -41691,37 +41685,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>2125</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A2" s="339" t="s">
+      <c r="A2" s="355" t="s">
         <v>2126</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="368" t="s">
+      <c r="A3" s="384" t="s">
         <v>2127</v>
       </c>
-      <c r="B3" s="369"/>
-      <c r="C3" s="369"/>
-      <c r="D3" s="369"/>
-      <c r="E3" s="369"/>
-      <c r="F3" s="369"/>
-      <c r="G3" s="370"/>
+      <c r="B3" s="385"/>
+      <c r="C3" s="385"/>
+      <c r="D3" s="385"/>
+      <c r="E3" s="385"/>
+      <c r="F3" s="385"/>
+      <c r="G3" s="386"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
       <c r="A4" s="143" t="s">
@@ -41736,11 +41730,11 @@
       <c r="D4" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="383" t="s">
+      <c r="E4" s="399" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="383"/>
-      <c r="G4" s="384"/>
+      <c r="F4" s="399"/>
+      <c r="G4" s="400"/>
     </row>
     <row r="5" spans="1:7" ht="65.25" customHeight="1">
       <c r="A5" s="131">
@@ -41755,11 +41749,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="345" t="s">
+      <c r="E5" s="361" t="s">
         <v>2130</v>
       </c>
-      <c r="F5" s="345"/>
-      <c r="G5" s="346"/>
+      <c r="F5" s="361"/>
+      <c r="G5" s="362"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="100"/>
@@ -41771,15 +41765,15 @@
       <c r="G6" s="100"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
-      <c r="A7" s="368" t="s">
+      <c r="A7" s="384" t="s">
         <v>2131</v>
       </c>
-      <c r="B7" s="369"/>
-      <c r="C7" s="369"/>
-      <c r="D7" s="369"/>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
-      <c r="G7" s="370"/>
+      <c r="B7" s="385"/>
+      <c r="C7" s="385"/>
+      <c r="D7" s="385"/>
+      <c r="E7" s="385"/>
+      <c r="F7" s="385"/>
+      <c r="G7" s="386"/>
     </row>
     <row r="8" spans="1:7" ht="24.75" customHeight="1">
       <c r="A8" s="145" t="s">
@@ -42063,37 +42057,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>2150</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="36.75" customHeight="1">
-      <c r="A2" s="367" t="s">
+      <c r="A2" s="383" t="s">
         <v>2151</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>2152</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="125" t="s">
@@ -42108,11 +42102,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="42" customHeight="1">
       <c r="A5" s="131">
@@ -42127,11 +42121,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>2155</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="39" customHeight="1">
       <c r="A6" s="131">
@@ -42146,11 +42140,11 @@
       <c r="D6" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="361" t="s">
         <v>2156</v>
       </c>
-      <c r="F6" s="345"/>
-      <c r="G6" s="346"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="362"/>
     </row>
     <row r="7" spans="1:7" ht="66.75" customHeight="1">
       <c r="A7" s="131">
@@ -42165,11 +42159,11 @@
       <c r="D7" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="E7" s="345" t="s">
+      <c r="E7" s="361" t="s">
         <v>2157</v>
       </c>
-      <c r="F7" s="345"/>
-      <c r="G7" s="346"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="362"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="100"/>
@@ -42181,15 +42175,15 @@
       <c r="G8" s="100"/>
     </row>
     <row r="9" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A9" s="338" t="s">
+      <c r="A9" s="354" t="s">
         <v>2158</v>
       </c>
-      <c r="B9" s="338"/>
-      <c r="C9" s="338"/>
-      <c r="D9" s="338"/>
-      <c r="E9" s="338"/>
-      <c r="F9" s="338"/>
-      <c r="G9" s="338"/>
+      <c r="B9" s="354"/>
+      <c r="C9" s="354"/>
+      <c r="D9" s="354"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
+      <c r="G9" s="354"/>
     </row>
     <row r="10" spans="1:7" ht="24" customHeight="1">
       <c r="A10" s="125" t="s">
@@ -42475,37 +42469,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>2172</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A2" s="339" t="s">
+      <c r="A2" s="355" t="s">
         <v>2173</v>
       </c>
-      <c r="B2" s="339"/>
-      <c r="C2" s="339"/>
-      <c r="D2" s="339"/>
-      <c r="E2" s="339"/>
-      <c r="F2" s="339"/>
-      <c r="G2" s="339"/>
+      <c r="B2" s="355"/>
+      <c r="C2" s="355"/>
+      <c r="D2" s="355"/>
+      <c r="E2" s="355"/>
+      <c r="F2" s="355"/>
+      <c r="G2" s="355"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>2174</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1">
       <c r="A4" s="125" t="s">
@@ -42520,11 +42514,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="105.75" customHeight="1">
       <c r="A5" s="131">
@@ -42539,11 +42533,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>2176</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="68.25" customHeight="1">
       <c r="A6" s="131">
@@ -42558,11 +42552,11 @@
       <c r="D6" s="132" t="s">
         <v>1716</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="361" t="s">
         <v>2178</v>
       </c>
-      <c r="F6" s="345"/>
-      <c r="G6" s="346"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="362"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="100"/>
@@ -42574,15 +42568,15 @@
       <c r="G7" s="100"/>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1">
-      <c r="A8" s="338" t="s">
+      <c r="A8" s="354" t="s">
         <v>2179</v>
       </c>
-      <c r="B8" s="338"/>
-      <c r="C8" s="338"/>
-      <c r="D8" s="338"/>
-      <c r="E8" s="338"/>
-      <c r="F8" s="338"/>
-      <c r="G8" s="338"/>
+      <c r="B8" s="354"/>
+      <c r="C8" s="354"/>
+      <c r="D8" s="354"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
+      <c r="G8" s="354"/>
     </row>
     <row r="9" spans="1:7" ht="28.5" customHeight="1">
       <c r="A9" s="125" t="s">
@@ -42867,35 +42861,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>2187</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A2" s="367"/>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="A2" s="383"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7" ht="33" customHeight="1">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>2188</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="33.75" customHeight="1">
       <c r="A4" s="125" t="s">
@@ -42910,11 +42904,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="109.5" customHeight="1">
       <c r="A5" s="131">
@@ -42929,11 +42923,11 @@
       <c r="D5" s="132" t="s">
         <v>2189</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>2190</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7" ht="90" customHeight="1">
       <c r="A6" s="131">
@@ -42948,11 +42942,11 @@
       <c r="D6" s="132" t="s">
         <v>2191</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="361" t="s">
         <v>2192</v>
       </c>
-      <c r="F6" s="345"/>
-      <c r="G6" s="346"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="362"/>
     </row>
     <row r="7" spans="1:7" ht="60" customHeight="1">
       <c r="A7" s="131">
@@ -42967,11 +42961,11 @@
       <c r="D7" s="132" t="s">
         <v>2193</v>
       </c>
-      <c r="E7" s="345" t="s">
+      <c r="E7" s="361" t="s">
         <v>2194</v>
       </c>
-      <c r="F7" s="345"/>
-      <c r="G7" s="346"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="362"/>
     </row>
     <row r="8" spans="1:7" ht="81.75" customHeight="1">
       <c r="A8" s="131">
@@ -42986,11 +42980,11 @@
       <c r="D8" s="132" t="s">
         <v>2196</v>
       </c>
-      <c r="E8" s="345" t="s">
+      <c r="E8" s="361" t="s">
         <v>2197</v>
       </c>
-      <c r="F8" s="345"/>
-      <c r="G8" s="346"/>
+      <c r="F8" s="361"/>
+      <c r="G8" s="362"/>
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" s="100"/>
@@ -43002,15 +42996,15 @@
       <c r="G9" s="100"/>
     </row>
     <row r="10" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A10" s="338" t="s">
+      <c r="A10" s="354" t="s">
         <v>2198</v>
       </c>
-      <c r="B10" s="338"/>
-      <c r="C10" s="338"/>
-      <c r="D10" s="338"/>
-      <c r="E10" s="338"/>
-      <c r="F10" s="338"/>
-      <c r="G10" s="338"/>
+      <c r="B10" s="354"/>
+      <c r="C10" s="354"/>
+      <c r="D10" s="354"/>
+      <c r="E10" s="354"/>
+      <c r="F10" s="354"/>
+      <c r="G10" s="354"/>
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" s="125" t="s">
@@ -43036,15 +43030,15 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15">
-      <c r="A12" s="338" t="s">
+      <c r="A12" s="354" t="s">
         <v>2199</v>
       </c>
-      <c r="B12" s="338"/>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
-      <c r="G12" s="338"/>
+      <c r="B12" s="354"/>
+      <c r="C12" s="354"/>
+      <c r="D12" s="354"/>
+      <c r="E12" s="354"/>
+      <c r="F12" s="354"/>
+      <c r="G12" s="354"/>
     </row>
     <row r="13" spans="1:7" ht="124.5" customHeight="1">
       <c r="A13" s="133">
@@ -43139,15 +43133,15 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="15">
-      <c r="A17" s="366" t="s">
+      <c r="A17" s="382" t="s">
         <v>2208</v>
       </c>
-      <c r="B17" s="366"/>
-      <c r="C17" s="366"/>
-      <c r="D17" s="366"/>
-      <c r="E17" s="366"/>
-      <c r="F17" s="366"/>
-      <c r="G17" s="366"/>
+      <c r="B17" s="382"/>
+      <c r="C17" s="382"/>
+      <c r="D17" s="382"/>
+      <c r="E17" s="382"/>
+      <c r="F17" s="382"/>
+      <c r="G17" s="382"/>
     </row>
     <row r="18" spans="1:7" ht="57.75">
       <c r="A18" s="133">
@@ -43283,24 +43277,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25">
-      <c r="A1" s="386" t="s">
+      <c r="A1" s="402" t="s">
         <v>2216</v>
       </c>
-      <c r="B1" s="387"/>
-      <c r="C1" s="387"/>
-      <c r="D1" s="387"/>
-      <c r="E1" s="387"/>
-      <c r="F1" s="388"/>
+      <c r="B1" s="403"/>
+      <c r="C1" s="403"/>
+      <c r="D1" s="403"/>
+      <c r="E1" s="403"/>
+      <c r="F1" s="404"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="389" t="s">
+      <c r="A2" s="405" t="s">
         <v>2217</v>
       </c>
-      <c r="B2" s="390"/>
-      <c r="C2" s="390"/>
-      <c r="D2" s="390"/>
-      <c r="E2" s="390"/>
-      <c r="F2" s="391"/>
+      <c r="B2" s="406"/>
+      <c r="C2" s="406"/>
+      <c r="D2" s="406"/>
+      <c r="E2" s="406"/>
+      <c r="F2" s="407"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="100"/>
@@ -43311,14 +43305,14 @@
       <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A4" s="392" t="s">
+      <c r="A4" s="408" t="s">
         <v>2218</v>
       </c>
-      <c r="B4" s="393"/>
-      <c r="C4" s="393"/>
-      <c r="D4" s="393"/>
-      <c r="E4" s="393"/>
-      <c r="F4" s="394"/>
+      <c r="B4" s="409"/>
+      <c r="C4" s="409"/>
+      <c r="D4" s="409"/>
+      <c r="E4" s="409"/>
+      <c r="F4" s="410"/>
     </row>
     <row r="5" spans="1:6" ht="20.25" customHeight="1">
       <c r="A5" s="161" t="s">
@@ -43385,14 +43379,14 @@
       <c r="F8" s="100"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1">
-      <c r="A9" s="392" t="s">
+      <c r="A9" s="408" t="s">
         <v>2225</v>
       </c>
-      <c r="B9" s="393"/>
-      <c r="C9" s="393"/>
-      <c r="D9" s="393"/>
-      <c r="E9" s="393"/>
-      <c r="F9" s="394"/>
+      <c r="B9" s="409"/>
+      <c r="C9" s="409"/>
+      <c r="D9" s="409"/>
+      <c r="E9" s="409"/>
+      <c r="F9" s="410"/>
     </row>
     <row r="10" spans="1:6" ht="29.25" customHeight="1">
       <c r="A10" s="161" t="s">
@@ -43522,37 +43516,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="342" t="s">
         <v>2238</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="326"/>
-      <c r="D1" s="326"/>
-      <c r="E1" s="326"/>
-      <c r="F1" s="326"/>
-      <c r="G1" s="326"/>
+      <c r="B1" s="342"/>
+      <c r="C1" s="342"/>
+      <c r="D1" s="342"/>
+      <c r="E1" s="342"/>
+      <c r="F1" s="342"/>
+      <c r="G1" s="342"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1">
-      <c r="A2" s="397" t="s">
+      <c r="A2" s="413" t="s">
         <v>2239</v>
       </c>
-      <c r="B2" s="397"/>
-      <c r="C2" s="397"/>
-      <c r="D2" s="397"/>
-      <c r="E2" s="397"/>
-      <c r="F2" s="397"/>
-      <c r="G2" s="397"/>
+      <c r="B2" s="413"/>
+      <c r="C2" s="413"/>
+      <c r="D2" s="413"/>
+      <c r="E2" s="413"/>
+      <c r="F2" s="413"/>
+      <c r="G2" s="413"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="326" t="s">
+      <c r="A3" s="342" t="s">
         <v>2218</v>
       </c>
-      <c r="B3" s="326"/>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="326"/>
-      <c r="F3" s="326"/>
-      <c r="G3" s="326"/>
+      <c r="B3" s="342"/>
+      <c r="C3" s="342"/>
+      <c r="D3" s="342"/>
+      <c r="E3" s="342"/>
+      <c r="F3" s="342"/>
+      <c r="G3" s="342"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="136" t="s">
@@ -43567,11 +43561,11 @@
       <c r="D4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="398" t="s">
+      <c r="E4" s="414" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="398"/>
-      <c r="G4" s="399"/>
+      <c r="F4" s="414"/>
+      <c r="G4" s="415"/>
     </row>
     <row r="5" spans="1:7" ht="71.25" customHeight="1">
       <c r="A5" s="138">
@@ -43586,11 +43580,11 @@
       <c r="D5" s="139" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="395" t="s">
+      <c r="E5" s="411" t="s">
         <v>2242</v>
       </c>
-      <c r="F5" s="395"/>
-      <c r="G5" s="396"/>
+      <c r="F5" s="411"/>
+      <c r="G5" s="412"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="89"/>
@@ -43602,15 +43596,15 @@
       <c r="G6" s="89"/>
     </row>
     <row r="7" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A7" s="326" t="s">
+      <c r="A7" s="342" t="s">
         <v>2225</v>
       </c>
-      <c r="B7" s="326"/>
-      <c r="C7" s="326"/>
-      <c r="D7" s="326"/>
-      <c r="E7" s="326"/>
-      <c r="F7" s="326"/>
-      <c r="G7" s="326"/>
+      <c r="B7" s="342"/>
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="342"/>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1">
       <c r="A8" s="136" t="s">
@@ -43636,15 +43630,15 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A9" s="326" t="s">
+      <c r="A9" s="342" t="s">
         <v>2243</v>
       </c>
-      <c r="B9" s="326"/>
-      <c r="C9" s="326"/>
-      <c r="D9" s="326"/>
-      <c r="E9" s="326"/>
-      <c r="F9" s="326"/>
-      <c r="G9" s="326"/>
+      <c r="B9" s="342"/>
+      <c r="C9" s="342"/>
+      <c r="D9" s="342"/>
+      <c r="E9" s="342"/>
+      <c r="F9" s="342"/>
+      <c r="G9" s="342"/>
     </row>
     <row r="10" spans="1:7" ht="102.75" customHeight="1">
       <c r="A10" s="150">
@@ -43753,34 +43747,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="347" t="s">
+      <c r="A1" s="363" t="s">
         <v>2248</v>
       </c>
-      <c r="B1" s="348"/>
-      <c r="C1" s="348"/>
-      <c r="D1" s="348"/>
-      <c r="E1" s="348"/>
-      <c r="F1" s="349"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="364"/>
+      <c r="D1" s="364"/>
+      <c r="E1" s="364"/>
+      <c r="F1" s="365"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="378" t="s">
+      <c r="A2" s="394" t="s">
         <v>2249</v>
       </c>
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="378"/>
-      <c r="F2" s="378"/>
+      <c r="B2" s="394"/>
+      <c r="C2" s="394"/>
+      <c r="D2" s="394"/>
+      <c r="E2" s="394"/>
+      <c r="F2" s="394"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="347" t="s">
+      <c r="A3" s="363" t="s">
         <v>2250</v>
       </c>
-      <c r="B3" s="348"/>
-      <c r="C3" s="348"/>
-      <c r="D3" s="348"/>
-      <c r="E3" s="348"/>
-      <c r="F3" s="349"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="365"/>
     </row>
     <row r="4" spans="1:6" ht="23.25" customHeight="1">
       <c r="A4" s="143" t="s">
@@ -43837,14 +43831,14 @@
       <c r="F6" s="132"/>
     </row>
     <row r="7" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A7" s="347" t="s">
+      <c r="A7" s="363" t="s">
         <v>2254</v>
       </c>
-      <c r="B7" s="348"/>
-      <c r="C7" s="348"/>
-      <c r="D7" s="348"/>
-      <c r="E7" s="348"/>
-      <c r="F7" s="349"/>
+      <c r="B7" s="364"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
+      <c r="E7" s="364"/>
+      <c r="F7" s="365"/>
     </row>
     <row r="8" spans="1:6" ht="36" customHeight="1">
       <c r="A8" s="143" t="s">
@@ -43956,37 +43950,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="354" t="s">
         <v>2260</v>
       </c>
-      <c r="B1" s="338"/>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="338"/>
-      <c r="F1" s="338"/>
-      <c r="G1" s="338"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
     </row>
     <row r="2" spans="1:7" ht="69.75" customHeight="1">
-      <c r="A2" s="367" t="s">
+      <c r="A2" s="383" t="s">
         <v>2261</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="338" t="s">
+      <c r="A3" s="354" t="s">
         <v>2250</v>
       </c>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
-      <c r="G3" s="338"/>
+      <c r="B3" s="354"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
       <c r="A4" s="125" t="s">
@@ -44001,11 +43995,11 @@
       <c r="D4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="368" t="s">
+      <c r="E4" s="384" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="369"/>
-      <c r="G4" s="370"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="386"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="131">
@@ -44020,11 +44014,11 @@
       <c r="D5" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="370" t="s">
         <v>2263</v>
       </c>
-      <c r="F5" s="354"/>
-      <c r="G5" s="355"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="371"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="100"/>
@@ -44036,15 +44030,15 @@
       <c r="G6" s="100"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="338" t="s">
+      <c r="A7" s="354" t="s">
         <v>2254</v>
       </c>
-      <c r="B7" s="338"/>
-      <c r="C7" s="338"/>
-      <c r="D7" s="338"/>
-      <c r="E7" s="338"/>
-      <c r="F7" s="338"/>
-      <c r="G7" s="338"/>
+      <c r="B7" s="354"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
+      <c r="G7" s="354"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="125" t="s">
@@ -44168,26 +44162,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6">
-      <c r="A1" s="400" t="s">
+      <c r="A1" s="416" t="s">
         <v>2271</v>
       </c>
-      <c r="B1" s="400"/>
-      <c r="C1" s="400"/>
-      <c r="D1" s="400"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="400"/>
+      <c r="B1" s="416"/>
+      <c r="C1" s="416"/>
+      <c r="D1" s="416"/>
+      <c r="E1" s="416"/>
+      <c r="F1" s="416"/>
+      <c r="G1" s="416"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="401" t="s">
+      <c r="A2" s="417" t="s">
         <v>2272</v>
       </c>
-      <c r="B2" s="401"/>
-      <c r="C2" s="401"/>
-      <c r="D2" s="401"/>
-      <c r="E2" s="401"/>
-      <c r="F2" s="401"/>
-      <c r="G2" s="401"/>
+      <c r="B2" s="417"/>
+      <c r="C2" s="417"/>
+      <c r="D2" s="417"/>
+      <c r="E2" s="417"/>
+      <c r="F2" s="417"/>
+      <c r="G2" s="417"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -45385,34 +45379,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="402" t="s">
+      <c r="A1" s="418" t="s">
         <v>2365</v>
       </c>
-      <c r="B1" s="403"/>
-      <c r="C1" s="403"/>
-      <c r="D1" s="403"/>
-      <c r="E1" s="403"/>
-      <c r="F1" s="404"/>
+      <c r="B1" s="419"/>
+      <c r="C1" s="419"/>
+      <c r="D1" s="419"/>
+      <c r="E1" s="419"/>
+      <c r="F1" s="420"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="405" t="s">
+      <c r="A2" s="421" t="s">
         <v>2366</v>
       </c>
-      <c r="B2" s="405"/>
-      <c r="C2" s="405"/>
-      <c r="D2" s="405"/>
-      <c r="E2" s="405"/>
-      <c r="F2" s="405"/>
+      <c r="B2" s="421"/>
+      <c r="C2" s="421"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="421"/>
+      <c r="F2" s="421"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="406" t="s">
+      <c r="A3" s="422" t="s">
         <v>2367</v>
       </c>
-      <c r="B3" s="406"/>
-      <c r="C3" s="406"/>
-      <c r="D3" s="406"/>
-      <c r="E3" s="406"/>
-      <c r="F3" s="406"/>
+      <c r="B3" s="422"/>
+      <c r="C3" s="422"/>
+      <c r="D3" s="422"/>
+      <c r="E3" s="422"/>
+      <c r="F3" s="422"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="163" t="s">
@@ -45455,14 +45449,14 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="402" t="s">
+      <c r="A6" s="418" t="s">
         <v>2372</v>
       </c>
-      <c r="B6" s="403"/>
-      <c r="C6" s="403"/>
-      <c r="D6" s="403"/>
-      <c r="E6" s="403"/>
-      <c r="F6" s="404"/>
+      <c r="B6" s="419"/>
+      <c r="C6" s="419"/>
+      <c r="D6" s="419"/>
+      <c r="E6" s="419"/>
+      <c r="F6" s="420"/>
     </row>
     <row r="7" spans="1:6" ht="25.5">
       <c r="A7" s="170" t="s">
@@ -45573,15 +45567,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="407" t="s">
+      <c r="A1" s="423" t="s">
         <v>2387</v>
       </c>
-      <c r="B1" s="407"/>
-      <c r="C1" s="407"/>
-      <c r="D1" s="407"/>
-      <c r="E1" s="407"/>
-      <c r="F1" s="407"/>
-      <c r="G1" s="407"/>
+      <c r="B1" s="423"/>
+      <c r="C1" s="423"/>
+      <c r="D1" s="423"/>
+      <c r="E1" s="423"/>
+      <c r="F1" s="423"/>
+      <c r="G1" s="423"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
@@ -45702,15 +45696,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="73.5" customHeight="1">
-      <c r="A1" s="408" t="s">
+      <c r="A1" s="424" t="s">
         <v>2395</v>
       </c>
-      <c r="B1" s="408"/>
-      <c r="C1" s="408"/>
-      <c r="D1" s="408"/>
-      <c r="E1" s="408"/>
-      <c r="F1" s="408"/>
-      <c r="G1" s="408"/>
+      <c r="B1" s="424"/>
+      <c r="C1" s="424"/>
+      <c r="D1" s="424"/>
+      <c r="E1" s="424"/>
+      <c r="F1" s="424"/>
+      <c r="G1" s="424"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
@@ -45736,15 +45730,15 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1">
-      <c r="A3" s="278" t="s">
+      <c r="A3" s="292" t="s">
         <v>2397</v>
       </c>
-      <c r="B3" s="278"/>
-      <c r="C3" s="278"/>
-      <c r="D3" s="278"/>
-      <c r="E3" s="278"/>
-      <c r="F3" s="278"/>
-      <c r="G3" s="278"/>
+      <c r="B3" s="292"/>
+      <c r="C3" s="292"/>
+      <c r="D3" s="292"/>
+      <c r="E3" s="292"/>
+      <c r="F3" s="292"/>
+      <c r="G3" s="292"/>
     </row>
     <row r="4" spans="1:7" ht="144.94999999999999">
       <c r="A4" s="52">
@@ -46026,15 +46020,15 @@
       <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A17" s="409" t="s">
+      <c r="A17" s="425" t="s">
         <v>2433</v>
       </c>
-      <c r="B17" s="409"/>
-      <c r="C17" s="409"/>
-      <c r="D17" s="409"/>
-      <c r="E17" s="409"/>
-      <c r="F17" s="409"/>
-      <c r="G17" s="409"/>
+      <c r="B17" s="425"/>
+      <c r="C17" s="425"/>
+      <c r="D17" s="425"/>
+      <c r="E17" s="425"/>
+      <c r="F17" s="425"/>
+      <c r="G17" s="425"/>
     </row>
     <row r="18" spans="1:7" ht="144.94999999999999">
       <c r="A18" s="52">
@@ -46313,7 +46307,7 @@
       </c>
       <c r="G30" s="450"/>
     </row>
-    <row r="31" spans="1:7" s="410" customFormat="1">
+    <row r="31" spans="1:7" s="426" customFormat="1">
       <c r="A31" s="453" t="s">
         <v>2440</v>
       </c>
@@ -46630,26 +46624,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="413" t="s">
+      <c r="A1" s="429" t="s">
         <v>2447</v>
       </c>
-      <c r="B1" s="414"/>
-      <c r="C1" s="414"/>
-      <c r="D1" s="414"/>
-      <c r="E1" s="414"/>
-      <c r="F1" s="414"/>
-      <c r="G1" s="415"/>
+      <c r="B1" s="430"/>
+      <c r="C1" s="430"/>
+      <c r="D1" s="430"/>
+      <c r="E1" s="430"/>
+      <c r="F1" s="430"/>
+      <c r="G1" s="431"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="284" t="s">
+      <c r="A2" s="298" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="286"/>
+      <c r="B2" s="299"/>
+      <c r="C2" s="299"/>
+      <c r="D2" s="299"/>
+      <c r="E2" s="299"/>
+      <c r="F2" s="299"/>
+      <c r="G2" s="300"/>
     </row>
     <row r="3" spans="1:7" ht="29.1">
       <c r="A3" s="22" t="s">
@@ -46687,11 +46681,11 @@
       <c r="D4" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="411" t="s">
+      <c r="E4" s="427" t="s">
         <v>2448</v>
       </c>
-      <c r="F4" s="411"/>
-      <c r="G4" s="412"/>
+      <c r="F4" s="427"/>
+      <c r="G4" s="428"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="26">
@@ -46706,11 +46700,11 @@
       <c r="D5" s="27" t="s">
         <v>2449</v>
       </c>
-      <c r="E5" s="411" t="s">
+      <c r="E5" s="427" t="s">
         <v>2450</v>
       </c>
-      <c r="F5" s="411"/>
-      <c r="G5" s="412"/>
+      <c r="F5" s="427"/>
+      <c r="G5" s="428"/>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="26">
@@ -46725,11 +46719,11 @@
       <c r="D6" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="411" t="s">
+      <c r="E6" s="427" t="s">
         <v>2451</v>
       </c>
-      <c r="F6" s="411"/>
-      <c r="G6" s="412"/>
+      <c r="F6" s="427"/>
+      <c r="G6" s="428"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="26">
@@ -46744,11 +46738,11 @@
       <c r="D7" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="E7" s="411" t="s">
+      <c r="E7" s="427" t="s">
         <v>2454</v>
       </c>
-      <c r="F7" s="411"/>
-      <c r="G7" s="412"/>
+      <c r="F7" s="427"/>
+      <c r="G7" s="428"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="26">
@@ -46763,11 +46757,11 @@
       <c r="D8" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="E8" s="411" t="s">
+      <c r="E8" s="427" t="s">
         <v>2457</v>
       </c>
-      <c r="F8" s="411"/>
-      <c r="G8" s="412"/>
+      <c r="F8" s="427"/>
+      <c r="G8" s="428"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="26">
@@ -46782,22 +46776,22 @@
       <c r="D9" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="E9" s="411" t="s">
+      <c r="E9" s="427" t="s">
         <v>2460</v>
       </c>
-      <c r="F9" s="411"/>
-      <c r="G9" s="412"/>
+      <c r="F9" s="427"/>
+      <c r="G9" s="428"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="284" t="s">
+      <c r="A10" s="298" t="s">
         <v>2461</v>
       </c>
-      <c r="B10" s="285"/>
-      <c r="C10" s="285"/>
-      <c r="D10" s="285"/>
-      <c r="E10" s="285"/>
-      <c r="F10" s="285"/>
-      <c r="G10" s="286"/>
+      <c r="B10" s="299"/>
+      <c r="C10" s="299"/>
+      <c r="D10" s="299"/>
+      <c r="E10" s="299"/>
+      <c r="F10" s="299"/>
+      <c r="G10" s="300"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="22" t="s">
@@ -47194,15 +47188,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15">
-      <c r="A1" s="416" t="s">
+      <c r="A1" s="432" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="417"/>
-      <c r="C1" s="417"/>
-      <c r="D1" s="417"/>
-      <c r="E1" s="417"/>
-      <c r="F1" s="417"/>
-      <c r="G1" s="418"/>
+      <c r="B1" s="433"/>
+      <c r="C1" s="433"/>
+      <c r="D1" s="433"/>
+      <c r="E1" s="433"/>
+      <c r="F1" s="433"/>
+      <c r="G1" s="434"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="234" t="s">
@@ -47240,20 +47234,20 @@
       <c r="D3" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="E3" s="419"/>
-      <c r="F3" s="419"/>
-      <c r="G3" s="420"/>
+      <c r="E3" s="435"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="436"/>
     </row>
     <row r="4" spans="1:7" ht="15">
-      <c r="A4" s="416" t="s">
+      <c r="A4" s="432" t="s">
         <v>2477</v>
       </c>
-      <c r="B4" s="417"/>
-      <c r="C4" s="417"/>
-      <c r="D4" s="417"/>
-      <c r="E4" s="417"/>
-      <c r="F4" s="417"/>
-      <c r="G4" s="418"/>
+      <c r="B4" s="433"/>
+      <c r="C4" s="433"/>
+      <c r="D4" s="433"/>
+      <c r="E4" s="433"/>
+      <c r="F4" s="433"/>
+      <c r="G4" s="434"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="234" t="s">
@@ -47398,96 +47392,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="432" t="s">
+      <c r="A1" s="279" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="432"/>
-      <c r="C1" s="432"/>
-      <c r="D1" s="432"/>
-      <c r="E1" s="432"/>
-      <c r="F1" s="432"/>
+      <c r="B1" s="279"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
     </row>
     <row r="2" spans="1:6" ht="45.75" customHeight="1">
-      <c r="A2" s="433" t="s">
+      <c r="A2" s="256" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="433" t="s">
+      <c r="B2" s="256" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="433" t="s">
+      <c r="C2" s="256" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="433" t="s">
+      <c r="D2" s="256" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="434" t="s">
+      <c r="E2" s="284" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="434"/>
+      <c r="F2" s="284"/>
     </row>
     <row r="3" spans="1:6" s="33" customFormat="1">
-      <c r="A3" s="435">
+      <c r="A3" s="257">
         <v>1</v>
       </c>
-      <c r="B3" s="435" t="s">
+      <c r="B3" s="257" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="435" t="s">
+      <c r="C3" s="257" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="435" t="s">
+      <c r="D3" s="257" t="s">
         <v>178</v>
       </c>
-      <c r="E3" s="436" t="s">
+      <c r="E3" s="280" t="s">
         <v>179</v>
       </c>
-      <c r="F3" s="436"/>
+      <c r="F3" s="280"/>
     </row>
     <row r="4" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A4" s="437">
+      <c r="A4" s="258">
         <v>2</v>
       </c>
-      <c r="B4" s="437" t="s">
+      <c r="B4" s="258" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="437" t="s">
+      <c r="C4" s="258" t="s">
         <v>180</v>
       </c>
-      <c r="D4" s="437" t="s">
+      <c r="D4" s="258" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="438" t="s">
+      <c r="E4" s="281" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="438"/>
+      <c r="F4" s="281"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="439" t="s">
+      <c r="A5" s="282" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="440"/>
-      <c r="C5" s="440"/>
-      <c r="D5" s="440"/>
-      <c r="E5" s="440"/>
-      <c r="F5" s="440"/>
+      <c r="B5" s="283"/>
+      <c r="C5" s="283"/>
+      <c r="D5" s="283"/>
+      <c r="E5" s="283"/>
+      <c r="F5" s="283"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="429" t="s">
+      <c r="A6" s="253" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="430" t="s">
+      <c r="B6" s="254" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="430" t="s">
+      <c r="C6" s="254" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="430" t="s">
+      <c r="D6" s="254" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="431" t="s">
+      <c r="E6" s="255" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="430" t="s">
+      <c r="F6" s="254" t="s">
         <v>49</v>
       </c>
     </row>
@@ -47972,14 +47966,14 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="255" t="s">
+      <c r="A31" s="265" t="s">
         <v>181</v>
       </c>
-      <c r="B31" s="256"/>
-      <c r="C31" s="256"/>
-      <c r="D31" s="256"/>
-      <c r="E31" s="256"/>
-      <c r="F31" s="256"/>
+      <c r="B31" s="266"/>
+      <c r="C31" s="266"/>
+      <c r="D31" s="266"/>
+      <c r="E31" s="266"/>
+      <c r="F31" s="266"/>
     </row>
     <row r="32" spans="1:6" s="33" customFormat="1">
       <c r="A32" s="28">
@@ -48425,15 +48419,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15">
-      <c r="A1" s="271" t="s">
+      <c r="A1" s="285" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="272"/>
-      <c r="C1" s="272"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="273"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="287"/>
     </row>
     <row r="2" spans="1:7" ht="15">
       <c r="A2" s="237" t="s">
@@ -48471,9 +48465,9 @@
       <c r="D3" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E3" s="280"/>
-      <c r="F3" s="280"/>
-      <c r="G3" s="281"/>
+      <c r="E3" s="294"/>
+      <c r="F3" s="294"/>
+      <c r="G3" s="295"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
       <c r="A4" s="9">
@@ -48488,11 +48482,11 @@
       <c r="D4" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="E4" s="280" t="s">
+      <c r="E4" s="294" t="s">
         <v>2491</v>
       </c>
-      <c r="F4" s="280"/>
-      <c r="G4" s="281"/>
+      <c r="F4" s="294"/>
+      <c r="G4" s="295"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="9">
@@ -48507,22 +48501,22 @@
       <c r="D5" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="E5" s="280" t="s">
+      <c r="E5" s="294" t="s">
         <v>2493</v>
       </c>
-      <c r="F5" s="280"/>
-      <c r="G5" s="281"/>
+      <c r="F5" s="294"/>
+      <c r="G5" s="295"/>
     </row>
     <row r="6" spans="1:7" ht="15">
-      <c r="A6" s="271" t="s">
+      <c r="A6" s="285" t="s">
         <v>2494</v>
       </c>
-      <c r="B6" s="272"/>
-      <c r="C6" s="272"/>
-      <c r="D6" s="272"/>
-      <c r="E6" s="272"/>
-      <c r="F6" s="272"/>
-      <c r="G6" s="273"/>
+      <c r="B6" s="286"/>
+      <c r="C6" s="286"/>
+      <c r="D6" s="286"/>
+      <c r="E6" s="286"/>
+      <c r="F6" s="286"/>
+      <c r="G6" s="287"/>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" s="237" t="s">
@@ -48778,15 +48772,15 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="15">
-      <c r="A18" s="421" t="s">
+      <c r="A18" s="437" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="422"/>
-      <c r="C18" s="422"/>
-      <c r="D18" s="422"/>
-      <c r="E18" s="422"/>
-      <c r="F18" s="422"/>
-      <c r="G18" s="423"/>
+      <c r="B18" s="438"/>
+      <c r="C18" s="438"/>
+      <c r="D18" s="438"/>
+      <c r="E18" s="438"/>
+      <c r="F18" s="438"/>
+      <c r="G18" s="439"/>
     </row>
     <row r="19" spans="1:7" ht="15">
       <c r="A19" s="9">
@@ -49019,15 +49013,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15">
-      <c r="A29" s="421" t="s">
+      <c r="A29" s="437" t="s">
         <v>181</v>
       </c>
-      <c r="B29" s="422"/>
-      <c r="C29" s="422"/>
-      <c r="D29" s="422"/>
-      <c r="E29" s="422"/>
-      <c r="F29" s="422"/>
-      <c r="G29" s="423"/>
+      <c r="B29" s="438"/>
+      <c r="C29" s="438"/>
+      <c r="D29" s="438"/>
+      <c r="E29" s="438"/>
+      <c r="F29" s="438"/>
+      <c r="G29" s="439"/>
     </row>
     <row r="30" spans="1:7" ht="15">
       <c r="A30" s="9">
@@ -49260,15 +49254,15 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15">
-      <c r="A40" s="271" t="s">
+      <c r="A40" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B40" s="272"/>
-      <c r="C40" s="272"/>
-      <c r="D40" s="272"/>
-      <c r="E40" s="272"/>
-      <c r="F40" s="272"/>
-      <c r="G40" s="273"/>
+      <c r="B40" s="286"/>
+      <c r="C40" s="286"/>
+      <c r="D40" s="286"/>
+      <c r="E40" s="286"/>
+      <c r="F40" s="286"/>
+      <c r="G40" s="287"/>
     </row>
     <row r="41" spans="1:7" ht="15">
       <c r="A41" s="9">
@@ -49501,15 +49495,15 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" customHeight="1">
-      <c r="A51" s="271" t="s">
+      <c r="A51" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B51" s="272"/>
-      <c r="C51" s="272"/>
-      <c r="D51" s="272"/>
-      <c r="E51" s="272"/>
-      <c r="F51" s="272"/>
-      <c r="G51" s="273"/>
+      <c r="B51" s="286"/>
+      <c r="C51" s="286"/>
+      <c r="D51" s="286"/>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+      <c r="G51" s="287"/>
     </row>
     <row r="52" spans="1:7" ht="15">
       <c r="A52" s="9">
@@ -49742,15 +49736,15 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1">
-      <c r="A62" s="271" t="s">
+      <c r="A62" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B62" s="272"/>
-      <c r="C62" s="272"/>
-      <c r="D62" s="272"/>
-      <c r="E62" s="272"/>
-      <c r="F62" s="272"/>
-      <c r="G62" s="273"/>
+      <c r="B62" s="286"/>
+      <c r="C62" s="286"/>
+      <c r="D62" s="286"/>
+      <c r="E62" s="286"/>
+      <c r="F62" s="286"/>
+      <c r="G62" s="287"/>
     </row>
     <row r="63" spans="1:7" ht="15">
       <c r="A63" s="9">
@@ -49983,15 +49977,15 @@
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
-      <c r="A73" s="271" t="s">
+      <c r="A73" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B73" s="272"/>
-      <c r="C73" s="272"/>
-      <c r="D73" s="272"/>
-      <c r="E73" s="272"/>
-      <c r="F73" s="272"/>
-      <c r="G73" s="273"/>
+      <c r="B73" s="286"/>
+      <c r="C73" s="286"/>
+      <c r="D73" s="286"/>
+      <c r="E73" s="286"/>
+      <c r="F73" s="286"/>
+      <c r="G73" s="287"/>
     </row>
     <row r="74" spans="1:7" ht="15">
       <c r="A74" s="9">
@@ -50224,15 +50218,15 @@
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1">
-      <c r="A84" s="271" t="s">
+      <c r="A84" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B84" s="272"/>
-      <c r="C84" s="272"/>
-      <c r="D84" s="272"/>
-      <c r="E84" s="272"/>
-      <c r="F84" s="272"/>
-      <c r="G84" s="273"/>
+      <c r="B84" s="286"/>
+      <c r="C84" s="286"/>
+      <c r="D84" s="286"/>
+      <c r="E84" s="286"/>
+      <c r="F84" s="286"/>
+      <c r="G84" s="287"/>
     </row>
     <row r="85" spans="1:7" ht="15">
       <c r="A85" s="9">
@@ -50465,15 +50459,15 @@
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" customHeight="1">
-      <c r="A95" s="271" t="s">
+      <c r="A95" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B95" s="272"/>
-      <c r="C95" s="272"/>
-      <c r="D95" s="272"/>
-      <c r="E95" s="272"/>
-      <c r="F95" s="272"/>
-      <c r="G95" s="273"/>
+      <c r="B95" s="286"/>
+      <c r="C95" s="286"/>
+      <c r="D95" s="286"/>
+      <c r="E95" s="286"/>
+      <c r="F95" s="286"/>
+      <c r="G95" s="287"/>
     </row>
     <row r="96" spans="1:7" ht="15">
       <c r="A96" s="9">
@@ -50706,15 +50700,15 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" customHeight="1">
-      <c r="A106" s="271" t="s">
+      <c r="A106" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B106" s="272"/>
-      <c r="C106" s="272"/>
-      <c r="D106" s="272"/>
-      <c r="E106" s="272"/>
-      <c r="F106" s="272"/>
-      <c r="G106" s="273"/>
+      <c r="B106" s="286"/>
+      <c r="C106" s="286"/>
+      <c r="D106" s="286"/>
+      <c r="E106" s="286"/>
+      <c r="F106" s="286"/>
+      <c r="G106" s="287"/>
     </row>
     <row r="107" spans="1:7" ht="15">
       <c r="A107" s="9">
@@ -50947,15 +50941,15 @@
       </c>
     </row>
     <row r="117" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A117" s="271" t="s">
+      <c r="A117" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B117" s="272"/>
-      <c r="C117" s="272"/>
-      <c r="D117" s="272"/>
-      <c r="E117" s="272"/>
-      <c r="F117" s="272"/>
-      <c r="G117" s="273"/>
+      <c r="B117" s="286"/>
+      <c r="C117" s="286"/>
+      <c r="D117" s="286"/>
+      <c r="E117" s="286"/>
+      <c r="F117" s="286"/>
+      <c r="G117" s="287"/>
     </row>
     <row r="118" spans="1:7" ht="15">
       <c r="A118" s="9">
@@ -51188,15 +51182,15 @@
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" customHeight="1">
-      <c r="A128" s="271" t="s">
+      <c r="A128" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B128" s="272"/>
-      <c r="C128" s="272"/>
-      <c r="D128" s="272"/>
-      <c r="E128" s="272"/>
-      <c r="F128" s="272"/>
-      <c r="G128" s="273"/>
+      <c r="B128" s="286"/>
+      <c r="C128" s="286"/>
+      <c r="D128" s="286"/>
+      <c r="E128" s="286"/>
+      <c r="F128" s="286"/>
+      <c r="G128" s="287"/>
     </row>
     <row r="129" spans="1:7" ht="15">
       <c r="A129" s="9">
@@ -51429,15 +51423,15 @@
       </c>
     </row>
     <row r="139" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A139" s="271" t="s">
+      <c r="A139" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B139" s="272"/>
-      <c r="C139" s="272"/>
-      <c r="D139" s="272"/>
-      <c r="E139" s="272"/>
-      <c r="F139" s="272"/>
-      <c r="G139" s="273"/>
+      <c r="B139" s="286"/>
+      <c r="C139" s="286"/>
+      <c r="D139" s="286"/>
+      <c r="E139" s="286"/>
+      <c r="F139" s="286"/>
+      <c r="G139" s="287"/>
     </row>
     <row r="140" spans="1:7" ht="15">
       <c r="A140" s="9">
@@ -51670,15 +51664,15 @@
       </c>
     </row>
     <row r="150" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A150" s="271" t="s">
+      <c r="A150" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B150" s="272"/>
-      <c r="C150" s="272"/>
-      <c r="D150" s="272"/>
-      <c r="E150" s="272"/>
-      <c r="F150" s="272"/>
-      <c r="G150" s="273"/>
+      <c r="B150" s="286"/>
+      <c r="C150" s="286"/>
+      <c r="D150" s="286"/>
+      <c r="E150" s="286"/>
+      <c r="F150" s="286"/>
+      <c r="G150" s="287"/>
     </row>
     <row r="151" spans="1:7" ht="15">
       <c r="A151" s="9">
@@ -51911,15 +51905,15 @@
       </c>
     </row>
     <row r="161" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A161" s="271" t="s">
+      <c r="A161" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B161" s="272"/>
-      <c r="C161" s="272"/>
-      <c r="D161" s="272"/>
-      <c r="E161" s="272"/>
-      <c r="F161" s="272"/>
-      <c r="G161" s="273"/>
+      <c r="B161" s="286"/>
+      <c r="C161" s="286"/>
+      <c r="D161" s="286"/>
+      <c r="E161" s="286"/>
+      <c r="F161" s="286"/>
+      <c r="G161" s="287"/>
     </row>
     <row r="162" spans="1:7" ht="15">
       <c r="A162" s="9">
@@ -52152,15 +52146,15 @@
       </c>
     </row>
     <row r="172" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A172" s="271" t="s">
+      <c r="A172" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B172" s="272"/>
-      <c r="C172" s="272"/>
-      <c r="D172" s="272"/>
-      <c r="E172" s="272"/>
-      <c r="F172" s="272"/>
-      <c r="G172" s="273"/>
+      <c r="B172" s="286"/>
+      <c r="C172" s="286"/>
+      <c r="D172" s="286"/>
+      <c r="E172" s="286"/>
+      <c r="F172" s="286"/>
+      <c r="G172" s="287"/>
     </row>
     <row r="173" spans="1:7" ht="15">
       <c r="A173" s="9">
@@ -52393,15 +52387,15 @@
       </c>
     </row>
     <row r="183" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A183" s="271" t="s">
+      <c r="A183" s="285" t="s">
         <v>181</v>
       </c>
-      <c r="B183" s="272"/>
-      <c r="C183" s="272"/>
-      <c r="D183" s="272"/>
-      <c r="E183" s="272"/>
-      <c r="F183" s="272"/>
-      <c r="G183" s="273"/>
+      <c r="B183" s="286"/>
+      <c r="C183" s="286"/>
+      <c r="D183" s="286"/>
+      <c r="E183" s="286"/>
+      <c r="F183" s="286"/>
+      <c r="G183" s="287"/>
     </row>
     <row r="184" spans="1:7" ht="15">
       <c r="A184" s="20">
@@ -52762,27 +52756,27 @@
     <row r="222" ht="15"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A84:G84"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A106:G106"/>
+    <mergeCell ref="A172:G172"/>
     <mergeCell ref="A183:G183"/>
     <mergeCell ref="A117:G117"/>
     <mergeCell ref="A128:G128"/>
     <mergeCell ref="A139:G139"/>
     <mergeCell ref="A150:G150"/>
     <mergeCell ref="A161:G161"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A106:G106"/>
-    <mergeCell ref="A172:G172"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52824,23 +52818,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="424" t="s">
+      <c r="A1" s="440" t="s">
         <v>2618</v>
       </c>
-      <c r="B1" s="425"/>
-      <c r="C1" s="425"/>
-      <c r="D1" s="425"/>
-      <c r="E1" s="426"/>
+      <c r="B1" s="441"/>
+      <c r="C1" s="441"/>
+      <c r="D1" s="441"/>
+      <c r="E1" s="442"/>
       <c r="F1" s="448"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="427" t="s">
+      <c r="A2" s="443" t="s">
         <v>2619</v>
       </c>
-      <c r="B2" s="427"/>
-      <c r="C2" s="427"/>
-      <c r="D2" s="427"/>
-      <c r="E2" s="427"/>
+      <c r="B2" s="443"/>
+      <c r="C2" s="443"/>
+      <c r="D2" s="443"/>
+      <c r="E2" s="443"/>
       <c r="F2" s="448"/>
     </row>
     <row r="3" spans="1:6">
@@ -52962,14 +52956,14 @@
       <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="428" t="s">
+      <c r="A10" s="444" t="s">
         <v>2637</v>
       </c>
-      <c r="B10" s="428"/>
-      <c r="C10" s="428"/>
-      <c r="D10" s="428"/>
-      <c r="E10" s="428"/>
-      <c r="F10" s="428"/>
+      <c r="B10" s="444"/>
+      <c r="C10" s="444"/>
+      <c r="D10" s="444"/>
+      <c r="E10" s="444"/>
+      <c r="F10" s="444"/>
     </row>
     <row r="11" spans="1:6" ht="30.75">
       <c r="A11" s="215" t="s">
@@ -53874,26 +53868,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A1" s="274" t="s">
+      <c r="A1" s="288" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="275"/>
-      <c r="C1" s="275"/>
-      <c r="D1" s="275"/>
-      <c r="E1" s="275"/>
-      <c r="F1" s="275"/>
-      <c r="G1" s="276"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="290"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="277" t="s">
+      <c r="A2" s="291" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="278"/>
-      <c r="C2" s="278"/>
-      <c r="D2" s="278"/>
-      <c r="E2" s="278"/>
-      <c r="F2" s="278"/>
-      <c r="G2" s="279"/>
+      <c r="B2" s="292"/>
+      <c r="C2" s="292"/>
+      <c r="D2" s="292"/>
+      <c r="E2" s="292"/>
+      <c r="F2" s="292"/>
+      <c r="G2" s="293"/>
     </row>
     <row r="3" spans="1:7" ht="29.1">
       <c r="A3" s="40" t="s">
@@ -53931,11 +53925,11 @@
       <c r="D4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="280" t="s">
+      <c r="E4" s="294" t="s">
         <v>234</v>
       </c>
-      <c r="F4" s="280"/>
-      <c r="G4" s="281"/>
+      <c r="F4" s="294"/>
+      <c r="G4" s="295"/>
     </row>
     <row r="5" spans="1:7" ht="36" customHeight="1">
       <c r="A5" s="41">
@@ -53950,22 +53944,22 @@
       <c r="D5" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="282" t="s">
+      <c r="E5" s="296" t="s">
         <v>236</v>
       </c>
-      <c r="F5" s="282"/>
-      <c r="G5" s="283"/>
+      <c r="F5" s="296"/>
+      <c r="G5" s="297"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="277" t="s">
+      <c r="A6" s="291" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="278"/>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="278"/>
-      <c r="G6" s="279"/>
+      <c r="B6" s="292"/>
+      <c r="C6" s="292"/>
+      <c r="D6" s="292"/>
+      <c r="E6" s="292"/>
+      <c r="F6" s="292"/>
+      <c r="G6" s="293"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="40" t="s">
@@ -53991,15 +53985,15 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="15">
-      <c r="A8" s="271" t="s">
+      <c r="A8" s="285" t="s">
         <v>238</v>
       </c>
-      <c r="B8" s="272"/>
-      <c r="C8" s="272"/>
-      <c r="D8" s="272"/>
-      <c r="E8" s="272"/>
-      <c r="F8" s="272"/>
-      <c r="G8" s="273"/>
+      <c r="B8" s="286"/>
+      <c r="C8" s="286"/>
+      <c r="D8" s="286"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="286"/>
+      <c r="G8" s="287"/>
     </row>
     <row r="9" spans="1:7" s="33" customFormat="1" ht="15">
       <c r="A9" s="228">
@@ -54508,15 +54502,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="14.45" customHeight="1">
-      <c r="A31" s="271" t="s">
+      <c r="A31" s="285" t="s">
         <v>263</v>
       </c>
-      <c r="B31" s="272"/>
-      <c r="C31" s="272"/>
-      <c r="D31" s="272"/>
-      <c r="E31" s="272"/>
-      <c r="F31" s="272"/>
-      <c r="G31" s="273"/>
+      <c r="B31" s="286"/>
+      <c r="C31" s="286"/>
+      <c r="D31" s="286"/>
+      <c r="E31" s="286"/>
+      <c r="F31" s="286"/>
+      <c r="G31" s="287"/>
     </row>
     <row r="32" spans="1:7" ht="15">
       <c r="A32" s="228">
@@ -55072,26 +55066,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31.5" customHeight="1">
-      <c r="A1" s="274" t="s">
+      <c r="A1" s="288" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="275"/>
-      <c r="C1" s="275"/>
-      <c r="D1" s="275"/>
-      <c r="E1" s="275"/>
-      <c r="F1" s="275"/>
-      <c r="G1" s="276"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="290"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="284" t="s">
+      <c r="A2" s="298" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="286"/>
+      <c r="B2" s="299"/>
+      <c r="C2" s="299"/>
+      <c r="D2" s="299"/>
+      <c r="E2" s="299"/>
+      <c r="F2" s="299"/>
+      <c r="G2" s="300"/>
     </row>
     <row r="3" spans="1:7" ht="43.5" customHeight="1">
       <c r="A3" s="192" t="s">
@@ -55106,11 +55100,11 @@
       <c r="D3" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="289" t="s">
+      <c r="E3" s="305" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="290"/>
-      <c r="G3" s="291"/>
+      <c r="F3" s="306"/>
+      <c r="G3" s="307"/>
     </row>
     <row r="4" spans="1:7" ht="48.75" customHeight="1">
       <c r="A4" s="193">
@@ -55125,11 +55119,11 @@
       <c r="D4" s="194" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="287" t="s">
+      <c r="E4" s="301" t="s">
         <v>274</v>
       </c>
-      <c r="F4" s="287"/>
-      <c r="G4" s="288"/>
+      <c r="F4" s="301"/>
+      <c r="G4" s="302"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="195">
@@ -55144,11 +55138,11 @@
       <c r="D5" s="42" t="s">
         <v>277</v>
       </c>
-      <c r="E5" s="269" t="s">
+      <c r="E5" s="303" t="s">
         <v>278</v>
       </c>
-      <c r="F5" s="269"/>
-      <c r="G5" s="270"/>
+      <c r="F5" s="303"/>
+      <c r="G5" s="304"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="196"/>
@@ -55160,15 +55154,15 @@
       <c r="G6" s="197"/>
     </row>
     <row r="7" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A7" s="284" t="s">
+      <c r="A7" s="298" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="285"/>
-      <c r="C7" s="285"/>
-      <c r="D7" s="285"/>
-      <c r="E7" s="285"/>
-      <c r="F7" s="285"/>
-      <c r="G7" s="286"/>
+      <c r="B7" s="299"/>
+      <c r="C7" s="299"/>
+      <c r="D7" s="299"/>
+      <c r="E7" s="299"/>
+      <c r="F7" s="299"/>
+      <c r="G7" s="300"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="192" t="s">
@@ -55437,6 +55431,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -55608,33 +55621,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C75CC7-3264-49B9-A7E5-314B8F17DD35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD798580-E728-431C-8751-C1407BFA2546}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD798580-E728-431C-8751-C1407BFA2546}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{169E7700-53E3-4F58-8B2B-1DA330E4A6F9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{169E7700-53E3-4F58-8B2B-1DA330E4A6F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C75CC7-3264-49B9-A7E5-314B8F17DD35}"/>
 </file>